--- a/jobsearch/pharmacy-jobs.xlsx
+++ b/jobsearch/pharmacy-jobs.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to use" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Active list'!$A$1:$AJ$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Active list'!$A$1:$AJ$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ46"/>
+  <dimension ref="A1:AJ39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Workday remote type 'Fully Remote'; text: 'Work is performed most of the time in an office or home office environment'; 'Excellent English language and grammar skills'. No work-authorisation sentence seen, but the role is listed under Johannesburg so South African residency/right to work is likely expected.</t>
+          <t>Workday remote type 'Fully Remote'; text: 'Work is performed most of the time in an office or home office environment'; 'Excellent English language and grammar skills'. No work-authorisation sentence seen, but the role is listed under Johannesburg so South African residency/right to work is likely expected. | Work-mode note: the description says 'office or home office'; the employer's data marks it remote.</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>Location 'Remote, Philippines'; no residency or licence wording.</t>
+          <t>Location 'Remote, Philippines'; no residency or licence wording. | Work-mode note: the description mentions an 'office environment'; the employer's data marks it remote.</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -2835,17 +2835,17 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Medical information / medical affairs / medical writing / HEOR &amp; market access</t>
+          <t>Clinical operations / clinical research</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Medical Writer III (Pharmacovigilance)</t>
+          <t>Clinical Research Intern - Portugal (Site Navigator Intern)</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Ergomed / PrimeVigilance</t>
+          <t>Fortrea</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>Zagreb, Croatia (remote)</t>
+          <t>Oeiras, Portugal (Workday remoteType: Remote)</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
@@ -2873,17 +2873,17 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>API location: Zagreb, Croatia, remote=true, hybrid=false. 'MD, pharmacy or Life Science degree (Masters or PhD is desirable)'. 'Fluency in English, an additional language is a benefit'. No work-authorisation sentence.</t>
+          <t>'Currently enrolled in or recently graduated from a University degree program in life sciences'; 'Fluent in local official language and in English'.</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>Minimum 2 years in medical writing and associated fields (case processing, signal detection or risk management), ideally in a CRO</t>
+          <t>None; demonstrated interest in clinical research</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>MD, pharmacy or life science degree (Master's/PhD desirable)</t>
+          <t>Currently enrolled in or recently graduated from a life-sciences degree programme</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>English fluent; additional language a benefit</t>
+          <t>Portuguese (local official language) and English</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
@@ -2903,40 +2903,42 @@
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>- Pharmacy/MD/life-science degree
-- Minimum 2 years in medical writing or associated PV fields
-- Ability to prioritise multiple tasks with attention to detail
-- Ability to train and mentor Associate Medical Writers
-- Team player
-- Fluent English</t>
+          <t>- Enrolled in or recently graduated from a life-sciences degree
+- Demonstrated interest in clinical research
+- Fluent Portuguese and English
+- Organisation and time management
+- Attention to detail
+- Microsoft Office proficiency
+- Handles confidential information</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>- Author, review and QC PSURs/PBRERs, PADERs, ACOs, DSURs and Risk Management Plans
-- Make sure documents are accurate, compliant and on time
-- Analyse and present safety data with cross-functional teams
-- Be client point of contact and mentor junior writers</t>
+          <t>- Support site start-up, activation, maintenance and closeout
+- Site identification and outreach, feasibility surveys
+- Collect and quality-review essential documents
+- Support ICF customisation and translation
+- Support CRA team preparing site initiation visits</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t>PSURs; PBRERs; DSURs; Risk Management Plans; pharmacovigilance; regulatory documents; medical writing; signal detection; case processing; quality check</t>
+          <t>site activation; feasibility; essential documents; informed consent forms; ICH-GCP; attention to detail; Microsoft Office; interest in clinical research</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t>Pharmacology and pharmacovigilance basics, evidence appraisal, regulatory-document literacy.</t>
+          <t>Life-science degree, regulatory/GCP concepts, consent materials.</t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t>2 years' medical-writing or PV experience; mentoring juniors; posting is tied to Croatia (employment location) although fully remote.</t>
+          <t>Portuguese fluency; 'recently graduated' may not cover a 2024 graduate; internship status.</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t>Pharmacy degree is explicitly welcome and the role is remote, but it needs 2 years in medical writing/PV and mentoring ability, which KT does not have yet.</t>
+          <t>Perfect task content for a first clinical-ops step and no experience needed; gaps are Portuguese fluency, Portugal location and whether a 2024 graduate counts as 'recently graduated'. Internship pay not stated.</t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
@@ -2946,12 +2948,12 @@
       </c>
       <c r="X16" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/Ergomed/744000155975969-medical-writer-iii-pharmacovigilance-?oga=true</t>
+          <t>https://fortrea.wd1.myworkdayjobs.com/Fortrea/job/Oeiras/Clinical-Research-Intern---Portugal_266202-1</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>Not stated (SmartRecruiters portal; CV)</t>
+          <t>CV via Workday portal</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
@@ -2985,12 +2987,12 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Clinical operations / clinical research</t>
+          <t>Medical information / medical affairs / medical writing / HEOR &amp; market access</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Clinical Research Intern - Portugal (Site Navigator Intern)</t>
+          <t>Medical Contact Center Associate I</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -3008,32 +3010,32 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Oeiras, Portugal (Workday remoteType: Remote)</t>
+          <t>Manila (Philippines)</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>remote</t>
+          <t>hybrid</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>unclear</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>'Currently enrolled in or recently graduated from a University degree program in life sciences'; 'Fluent in local official language and in English'.</t>
+          <t>Location Manila; 'Physical Demands/Work Environment: Office Environment or remote.' Qualifications: 'Bachelor's or Master's in Pharmacy or Life Science or Medical Science or related area + 1 to 2 years of safety experience.' No licence required for this Associate I posting. | Audit: the posting states no residency or work-authorisation rule (the 'no' is an inference from the Manila location). Work mode is flagged hybrid, but the body says 'Office Environment or remote'.</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>None; demonstrated interest in clinical research</t>
+          <t>1 to 2 years of safety experience (AE/SAE processing, narratives, safety databases)</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>Currently enrolled in or recently graduated from a life-sciences degree programme</t>
+          <t>Bachelor's/Master's in Pharmacy, Life Science, Medical Science or related</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
@@ -3043,7 +3045,7 @@
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>Portuguese (local official language) and English</t>
+          <t>English (good written and verbal communication); not otherwise stated</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
@@ -3053,42 +3055,41 @@
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t>- Enrolled in or recently graduated from a life-sciences degree
-- Demonstrated interest in clinical research
-- Fluent Portuguese and English
-- Organisation and time management
-- Attention to detail
-- Microsoft Office proficiency
-- Handles confidential information</t>
+          <t>- Pharmacy/life science degree
+- 1-2 years of safety experience
+- Good written and verbal communication
+- Ability to receive/manage inbound and outbound calls
+- Understanding of PV regulations, GVP and ICH GCP
+- Microsoft Office
+- High accuracy and attention to detail</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>- Support site start-up, activation, maintenance and closeout
-- Site identification and outreach, feasibility surveys
-- Collect and quality-review essential documents
-- Support ICF customisation and translation
-- Support CRA team preparing site initiation visits</t>
+          <t>- Answer medical information queries, product quality complaints and general queries by phone, email, fax
+- Record and report adverse drug reactions within timelines
+- Run drug safety data management steps (call intake, documentation, peer review, follow-up)
+- Track metrics, QC steps, training and data reconciliation</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t>site activation; feasibility; essential documents; informed consent forms; ICH-GCP; attention to detail; Microsoft Office; interest in clinical research</t>
+          <t>medical information queries; product quality complaints; Adverse Drug Reaction; drug safety data management; call intake; case follow-up; pharmacovigilance practices; ICH GCP; quality of data; reconciliation of data</t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t>Life-science degree, regulatory/GCP concepts, consent materials.</t>
+          <t>Pharmacology, adverse drug reaction recognition, drug-information answering, regulatory (GVP/GCP) awareness.</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t>Portuguese fluency; 'recently graduated' may not cover a 2024 graduate; internship status.</t>
+          <t>1-2 years of safety/AE processing experience; located in the Philippines; call-handling experience helps.</t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t>Perfect task content for a first clinical-ops step and no experience needed; gaps are Portuguese fluency, Portugal location and whether a 2024 graduate counts as 'recently graduated'. Internship pay not stated.</t>
+          <t>Pharmacy degree is the stated education; the gap is 1-2 years of safety experience and being in Manila (hybrid). Two sister postings (Assistant I and call-center Associate I) in Manila need a healthcare licence and voice call-centre experience, so this is the only one of the three KT could reach.</t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
@@ -3098,12 +3099,12 @@
       </c>
       <c r="X17" s="4" t="inlineStr">
         <is>
-          <t>https://fortrea.wd1.myworkdayjobs.com/Fortrea/job/Oeiras/Clinical-Research-Intern---Portugal_266202-1</t>
+          <t>https://fortrea.wd1.myworkdayjobs.com/Fortrea/job/Manila/Medical-Contact-Center-Associate-I_266007/apply</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>CV via Workday portal</t>
+          <t>Not stated (Workday portal; CV)</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
@@ -3137,17 +3138,17 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Medical information / medical affairs / medical writing / HEOR &amp; market access</t>
+          <t>Regulatory Affairs / Quality / Labelling / GxP</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Medical Contact Center Associate I</t>
+          <t>Regulatory and Start Up Specialist - Netherlands (Clinical FSP)</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Fortrea</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -3160,32 +3161,32 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>Manila (Philippines)</t>
+          <t>Amsterdam, Netherlands (also Leiden, Utrecht, Heerlen)</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>hybrid</t>
+          <t>unclear</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>unclear</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>Location Manila; 'Physical Demands/Work Environment: Office Environment or remote.' Qualifications: 'Bachelor's or Master's in Pharmacy or Life Science or Medical Science or related area + 1 to 2 years of safety experience.' No licence required for this Associate I posting.</t>
+          <t>'Fluency in Dutch with strong English communication skills.' Work mode not stated in the text (Workday remoteType empty).</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>1 to 2 years of safety experience (AE/SAE processing, narratives, safety databases)</t>
+          <t>Experience in clinical trial regulatory affairs, site start-up, site activation or related clinical research functions (number of years not stated)</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>Bachelor's/Master's in Pharmacy, Life Science, Medical Science or related</t>
+          <t>Bachelor's Degree in Life Sciences or a related scientific discipline</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
@@ -3195,7 +3196,7 @@
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>English (good written and verbal communication); not otherwise stated</t>
+          <t>Dutch (fluent) and English</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
@@ -3205,41 +3206,41 @@
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>- Pharmacy/life science degree
-- 1-2 years of safety experience
-- Good written and verbal communication
-- Ability to receive/manage inbound and outbound calls
-- Understanding of PV regulations, GVP and ICH GCP
-- Microsoft Office
-- High accuracy and attention to detail</t>
+          <t>- Bachelor's in life sciences or related
+- Experience in clinical trial regulatory affairs, site start-up or site activation
+- Understanding of local and international regulatory requirements, GCP
+- Experience managing regulatory documentation, contracts and start-up deliverables
+- Communication, negotiation and problem solving
+- Fluent Dutch and strong English</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>- Answer medical information queries, product quality complaints and general queries by phone, email, fax
-- Record and report adverse drug reactions within timelines
-- Run drug safety data management steps (call intake, documentation, peer review, follow-up)
-- Track metrics, QC steps, training and data reconciliation</t>
+          <t>- Site identification, feasibility and site activation for assigned studies
+- Prepare and track regulatory, ethics committee, ICF and investigator pack submissions
+- Review and negotiate site contracts (CTAs)
+- Quality review of site documentation
+- Provide local regulatory expertise to project teams</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t>medical information queries; product quality complaints; Adverse Drug Reaction; drug safety data management; call intake; case follow-up; pharmacovigilance practices; ICH GCP; quality of data; reconciliation of data</t>
+          <t>regulatory submissions; ethics committee submissions; site activation; GCP; clinical trial agreements; essential documents; informed consent forms; study start-up; regulatory documentation</t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t>Pharmacology, adverse drug reaction recognition, drug-information answering, regulatory (GVP/GCP) awareness.</t>
+          <t>GCP, trial regulation and consent concepts, life sciences degree.</t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t>1-2 years of safety/AE processing experience; located in the Philippines; call-handling experience helps.</t>
+          <t>Fluent Dutch needed; no start-up or regulatory experience; work mode not stated.</t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t>Pharmacy degree is the stated education; the gap is 1-2 years of safety experience and being in Manila (hybrid). Two sister postings (Assistant I and call-center Associate I) in Manila need a healthcare licence and voice call-centre experience, so this is the only one of the three KT could reach.</t>
+          <t>Years of experience are not stated, but clinical-trial regulatory/start-up experience is expected and Dutch fluency is required. The language is the main gap.</t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
@@ -3249,12 +3250,12 @@
       </c>
       <c r="X18" s="4" t="inlineStr">
         <is>
-          <t>https://fortrea.wd1.myworkdayjobs.com/Fortrea/job/Manila/Medical-Contact-Center-Associate-I_266007/apply</t>
+          <t>https://iqvia.wd1.myworkdayjobs.com/IQVIA/job/Amsterdam-Netherlands/Regulatory-and-Start-Up-Specialist---Netherlands_R1547012</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t>Not stated (Workday portal; CV)</t>
+          <t>Not stated (Workday portal; CV expected)</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
@@ -3288,17 +3289,17 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Pharmacovigilance / Drug Safety</t>
+          <t>Regulatory Affairs / Quality / Labelling / GxP</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Clinical Trial Safety Scientist (FSP - Permanent Home Based)</t>
+          <t>INGENYX - Regulatory Affairs Specialist (labeling, UDI and regulatory data)</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>IQVIA</t>
+          <t>Ingenyx (former Teleflex contract-manufacturing business; hosted on the Teleflex careers site)</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -3311,12 +3312,12 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>Madrid, Spain; Barcelona, Spain (home-based)</t>
+          <t>Remote, MA, US</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>home-based</t>
+          <t>remote</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -3326,17 +3327,17 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>Locations Madrid/Barcelona, Spain only; permanent home-based; no visa wording on the page.</t>
+          <t>'Location: Remote, MA, US'; expected travel up to 10%. No residency or work-authorisation wording on the page. Pay range is in US dollars and refers to US benefits (401k).</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>'Minimum 2+ years of experience in Pharmacovigilance / Drug Safety'</t>
+          <t>2-5 years of Regulatory Affairs or medical device experience preferred</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>'Educational degree (BSc/Msc/PhD) in Life Science or equivalent work experience in directly related fields'</t>
+          <t>Bachelor's degree in Regulatory Affairs, Life Sciences, Engineering, Quality or related field; equivalent relevant experience may be considered</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
@@ -3346,53 +3347,51 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>Not stated (Spanish likely useful but not stated)</t>
+          <t>English</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>not stated</t>
+          <t>$87,400.00 - $131,100.00 expected base pay range</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>- Life-science degree (BSc/MSc/PhD) or equivalent experience
-- Minimum 2+ years in PV / drug safety
-- Understanding of the clinical study and drug development process
-- Knowledge of ICH/GCP
-- Knowledge of SAE reporting requirements
-- Data review tools experience preferred
-- Analytical skills and ability to summarise complex information
-- Time management</t>
+          <t>- Bachelor's in Regulatory Affairs, Life Sciences, Engineering, Quality or related field
+- 2-5 years RA or medical device experience preferred
+- Working knowledge of US and/or international medical device regulatory requirements
+- Medical device labeling and UDI experience strongly preferred
+- Familiarity with FDA GUDID, EU EUDAMED, GS1, GTINs, GLNs, GDSN preferred
+- Attention to detail, organisation, analytical thinking</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>- Review patient-level clinical and safety data for medical accuracy, coding consistency and generate queries
-- Prepare aggregated data visualisation and facilitate study-level safety review meetings
-- Contribute to study start-up activities
-- Support medical evaluation with study physicians
-- Escalate urgent medical cases; contribute to patient narrative processes</t>
+          <t>- Create, revise and maintain medical device labeling, IFUs and symbols
+- Support UDI assignment and maintenance (GTIN, UDI-DI, UDI-PI) and update GUDID/EUDAMED
+- Maintain regulatory product data and registrations
+- Support submissions, renewals, notifications and market maintenance
+- Support audits, Notified Body and authority requests</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t>Pharmacovigilance / Drug Safety; ICH/GCP guidelines; SAE reporting requirements; patient-level clinical/safety data; coding consistency; patient narratives; drug development process; data review tools; queries</t>
+          <t>labeling; UDI; regulatory product data; regulatory submissions; registrations and renewals; regulatory impact assessment; attention to detail; cross-functional teams; health authority databases; life sciences</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t>Clinical pharmacology, GCP awareness, medical review of safety data and coding.</t>
+          <t>Labelling and packaging information (SmPC/PIL concepts), regulatory frameworks, pharmacovigilance and product information accuracy.</t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t>2+ years PV experience; Spain location; no data-review tool experience.</t>
+          <t>No device labeling or UDI experience; US location and no statement on work authorisation, so likely US residents only.</t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t>Needs 2+ years of PV experience (clear gap) but an MPharm meets the degree line and the role is home-based within a CRO FSP model.</t>
+          <t>Experience is 'preferred' (2-5 years) and equivalent experience is considered, so a graduate could be considered, but medical-device labeling/UDI experience is strongly preferred and the role is US-based (Massachusetts).</t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
@@ -3402,12 +3401,12 @@
       </c>
       <c r="X19" s="4" t="inlineStr">
         <is>
-          <t>https://iqvia.wd1.myworkdayjobs.com/IQVIA/job/Madrid-Spain/Clinical-Trial-Safety-Scientist--FSP---Permanent-Home-Based-_R1521994/apply?source=APPLICANT_SOURCE-3-2025</t>
+          <t>https://careers.teleflex.com/talentcommunity/apply/1440918700/?locale=en_US</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t>Workday application; no other documents stated</t>
+          <t>Not stated (portal application; CV expected)</t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
@@ -3441,17 +3440,17 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Regulatory Affairs / Quality / Labelling / GxP</t>
+          <t>Pharmacovigilance / Drug Safety</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Regulatory and Start Up Specialist - Netherlands (Clinical FSP)</t>
+          <t>Senior Benefit/Risk Associate (signal detection)</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>IQVIA</t>
+          <t>PrimeVigilance (Ergomed Group)</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -3464,32 +3463,32 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>Amsterdam, Netherlands (also Leiden, Utrecht, Heerlen)</t>
+          <t>Warsaw, Poland (remote flag)</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
+          <t>remote</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
           <t>unclear</t>
         </is>
       </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>unclear</t>
-        </is>
-      </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>'Fluency in Dutch with strong English communication skills.' Work mode not stated in the text (Workday remoteType empty).</t>
+          <t>Location Warsaw, Poland; 'Advanced proficiency in English, both verbal and written (minimum B2 level)'. No visa wording.</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>Experience in clinical trial regulatory affairs, site start-up, site activation or related clinical research functions (number of years not stated)</t>
+          <t>'Demonstrated previous experience in signal detection is strongly preferred' (no minimum years stated)</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>Bachelor's Degree in Life Sciences or a related scientific discipline</t>
+          <t>'Educational background in Life Sciences or Biomedical fields (Pharmacy degree preferred)'</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
@@ -3499,7 +3498,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>Dutch (fluent) and English</t>
+          <t>English B2 minimum (advanced)</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
@@ -3509,41 +3508,41 @@
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t>- Bachelor's in life sciences or related
-- Experience in clinical trial regulatory affairs, site start-up or site activation
-- Understanding of local and international regulatory requirements, GCP
-- Experience managing regulatory documentation, contracts and start-up deliverables
-- Communication, negotiation and problem solving
-- Fluent Dutch and strong English</t>
+          <t>- Life sciences or biomedical background; pharmacy degree preferred
+- Signal detection experience strongly preferred
+- Commitment to patient safety and willingness to learn
+- Time and issue management, multitasking, attention to detail
+- Interpersonal and communication skills
+- English B2 or above</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>- Site identification, feasibility and site activation for assigned studies
-- Prepare and track regulatory, ethics committee, ICF and investigator pack submissions
-- Review and negotiate site contracts (CTAs)
-- Quality review of site documentation
-- Provide local regulatory expertise to project teams</t>
+          <t>- Take part in signal detection activities including set-up
+- Review line listings for signal detection reports
+- Draft signal detection reports with quality control
+- Evaluate and categorise potential signals and propose actions
+- Support communications with regulatory authorities</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t>regulatory submissions; ethics committee submissions; site activation; GCP; clinical trial agreements; essential documents; informed consent forms; study start-up; regulatory documentation</t>
+          <t>signal detection; line listings; signal detection report; evaluating and categorizing potential signals; benefit-risk; pharmacovigilance; patient safety; attention to detail</t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t>GCP, trial regulation and consent concepts, life sciences degree.</t>
+          <t>Pharmacy degree preferred; pharmacology, pharmacoepidemiology and benefit-risk thinking apply directly.</t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t>Fluent Dutch needed; no start-up or regulatory experience; work mode not stated.</t>
+          <t>No signal detection experience; Poland location; 'Senior' title.</t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t>Years of experience are not stated, but clinical-trial regulatory/start-up experience is expected and Dutch fluency is required. The language is the main gap.</t>
+          <t>Posting says a pharmacy degree is preferred and states no minimum years, which suits an MPharm graduate; signal detection experience is strongly preferred, the gap. Poland-based remote.</t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
@@ -3553,12 +3552,12 @@
       </c>
       <c r="X20" s="4" t="inlineStr">
         <is>
-          <t>https://iqvia.wd1.myworkdayjobs.com/IQVIA/job/Amsterdam-Netherlands/Regulatory-and-Start-Up-Specialist---Netherlands_R1547012</t>
+          <t>https://jobs.smartrecruiters.com/Ergomed/744000155975030-senior-benefit-risk-associate?oga=true</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t>Not stated (Workday portal; CV expected)</t>
+          <t>Online application on SmartRecruiters; no other documents stated</t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
@@ -3597,12 +3596,12 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>INGENYX - Regulatory Affairs Specialist (labeling, UDI and regulatory data)</t>
+          <t>Quality Specialist (GxP eQMS: deviations, CAPA, audits)</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Ingenyx (former Teleflex contract-manufacturing business; hosted on the Teleflex careers site)</t>
+          <t>ProPharma Group</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -3615,12 +3614,12 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>Remote, MA, US</t>
+          <t>India</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>remote</t>
+          <t>unclear</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -3630,17 +3629,17 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>'Location: Remote, MA, US'; expected travel up to 10%. No residency or work-authorisation wording on the page. Pay range is in US dollars and refers to US benefits (401k).</t>
+          <t>Location 'India' only; Workday remoteType empty. Footer: 'Whilst ProPharma supports remote working ... we encourage any new hires that are based within a reasonably short commute of one of our offices to work on a hybrid basis'. 'Fluent in English speaking and writing.'</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>2-5 years of Regulatory Affairs or medical device experience preferred</t>
+          <t>Minimum 2 years in a Quality Assurance role; deviation, quality event, CAPA, effectiveness check experience</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>Bachelor's degree in Regulatory Affairs, Life Sciences, Engineering, Quality or related field; equivalent relevant experience may be considered</t>
+          <t>University/bachelor's degree and/or appropriate relevant work experience</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
@@ -3650,51 +3649,52 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>English (fluent)</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>$87,400.00 - $131,100.00 expected base pay range</t>
+          <t>not stated</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t>- Bachelor's in Regulatory Affairs, Life Sciences, Engineering, Quality or related field
-- 2-5 years RA or medical device experience preferred
-- Working knowledge of US and/or international medical device regulatory requirements
-- Medical device labeling and UDI experience strongly preferred
-- Familiarity with FDA GUDID, EU EUDAMED, GS1, GTINs, GLNs, GDSN preferred
-- Attention to detail, organisation, analytical thinking</t>
+          <t>- Bachelor's degree and/or relevant work experience
+- 2+ years in a QA role
+- Knowledge and experience of GxP Quality Management Systems
+- Deviation, Quality Event, CAPA and effectiveness check experience
+- Fluent English
+- Strong organisation and attention to detail
+- Proficient Microsoft Office</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>- Create, revise and maintain medical device labeling, IFUs and symbols
-- Support UDI assignment and maintenance (GTIN, UDI-DI, UDI-PI) and update GUDID/EUDAMED
-- Maintain regulatory product data and registrations
-- Support submissions, renewals, notifications and market maintenance
-- Support audits, Notified Body and authority requests</t>
+          <t>- Support and run eQMS activities (change control, deviations, quality events, CAPAs, effectiveness checks)
+- Support client audits and regulatory inspections and track audit CAPA responses
+- Analyse deviations and quality events and report quality KPIs
+- Take part in GxP change management and risk/impact analysis
+- Medical-information-specific: evaluate call and case-report quality against compliance standards</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t>labeling; UDI; regulatory product data; regulatory submissions; registrations and renewals; regulatory impact assessment; attention to detail; cross-functional teams; health authority databases; life sciences</t>
+          <t>GxP; eQMS; change control; deviations; CAPA; quality events; effectiveness checks; audits and inspections; quality KPIs; root cause</t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t>Labelling and packaging information (SmPC/PIL concepts), regulatory frameworks, pharmacovigilance and product information accuracy.</t>
+          <t>GMP/GxP principles, quality management, CAPA and deviation concepts, regulatory inspection awareness.</t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t>No device labeling or UDI experience; US location and no statement on work authorisation, so likely US residents only.</t>
+          <t>No QA industry experience; work mode and non-resident eligibility not clear from the posting (India listing).</t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t>Experience is 'preferred' (2-5 years) and equivalent experience is considered, so a graduate could be considered, but medical-device labeling/UDI experience is strongly preferred and the role is US-based (Massachusetts).</t>
+          <t>A bachelor's is enough on education, but 2 years of QA experience in a GxP setting is asked. One clear gap (experience).</t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
@@ -3704,12 +3704,12 @@
       </c>
       <c r="X21" s="4" t="inlineStr">
         <is>
-          <t>https://careers.teleflex.com/talentcommunity/apply/1440918700/?locale=en_US</t>
+          <t>https://propharmagroup.wd1.myworkdayjobs.com/ppgcareers/job/India/Quality-Specialist_JR10726</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t>Not stated (portal application; CV expected)</t>
+          <t>Not stated (Workday portal; CV expected)</t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
@@ -3743,17 +3743,17 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Pharmacovigilance / Drug Safety</t>
+          <t>Clinical operations / clinical research</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Senior Benefit/Risk Associate (signal detection)</t>
+          <t>FSP Clinical Trial Coordinator (Sweden, remote)</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>PrimeVigilance (Ergomed Group)</t>
+          <t>Thermo Fisher Scientific (PPD clinical research business)</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>Warsaw, Poland (remote flag)</t>
+          <t>Sweden - Stockholm - Remote</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
@@ -3781,17 +3781,17 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>Location Warsaw, Poland; 'Advanced proficiency in English, both verbal and written (minimum B2 level)'. No visa wording.</t>
+          <t>'Hybrid work if located in Copenhagen or Stockholm... If other location, it will be a remote work setting'; 'proficient local language skills (Swedish or Danish)'; Workday remoteType Fully Remote. | Work-mode note: hybrid if based in Stockholm or Copenhagen, remote otherwise.</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>'Demonstrated previous experience in signal detection is strongly preferred' (no minimum years stated)</t>
+          <t>0 to 1 year (equivalency considered)</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>'Educational background in Life Sciences or Biomedical fields (Pharmacy degree preferred)'</t>
+          <t>High/secondary school diploma plus relevant qualification; bachelor's preferred</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>English B2 minimum (advanced)</t>
+          <t>English plus Swedish or Danish</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
@@ -3811,41 +3811,43 @@
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t>- Life sciences or biomedical background; pharmacy degree preferred
-- Signal detection experience strongly preferred
-- Commitment to patient safety and willingness to learn
-- Time and issue management, multitasking, attention to detail
-- Interpersonal and communication skills
-- English B2 or above</t>
+          <t>- Secondary diploma and relevant qualification; bachelor's preferred
+- About 0-1 year of relevant experience
+- Good English plus proficient Swedish or Danish
+- Working knowledge of ICH GCP and country regulations (to be developed)
+- Good organisational skills and attention to detail
+- Proficient in MS Office
+- Able to learn clinical trial database systems
+- Able to complete the company clinical training programme</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>- Take part in signal detection activities including set-up
-- Review line listings for signal detection reports
-- Draft signal detection reports with quality control
-- Evaluate and categorise potential signals and propose actions
-- Support communications with regulatory authorities</t>
+          <t>- Administrative and technical support to the project team
+- Support site activation and site lists/feasibility
+- Process documents to (e)TMF and perform TMF reviews
+- Distribute Investigator Site File and pharmacy binder materials
+- Run study metric reconciliation and findings reports</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t>signal detection; line listings; signal detection report; evaluating and categorizing potential signals; benefit-risk; pharmacovigilance; patient safety; attention to detail</t>
+          <t>Trial Master File; eTMF; site activation; feasibility; Investigator Site File; ICH GCP; MS Office; attention to detail; organisational skills</t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t>Pharmacy degree preferred; pharmacology, pharmacoepidemiology and benefit-risk thinking apply directly.</t>
+          <t>Degree-level science background, documentation and regulatory awareness, GCP concepts.</t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t>No signal detection experience; Poland location; 'Senior' title.</t>
+          <t>Swedish or Danish language; no industry experience.</t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t>Posting says a pharmacy degree is preferred and states no minimum years, which suits an MPharm graduate; signal detection experience is strongly preferred, the gap. Poland-based remote.</t>
+          <t>Experience bar is only 0-1 year and degree preferred, but fluency in Swedish or Danish is required, which is a clear gap unless KT speaks one.</t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
@@ -3855,12 +3857,12 @@
       </c>
       <c r="X22" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/Ergomed/744000155975030-senior-benefit-risk-associate?oga=true</t>
+          <t>https://thermofisher.wd5.myworkdayjobs.com/ThermoFisherCareers/job/Remote-Sweden/FSP-Clinical-Trial-Coordinator_R-01369781</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t>Online application on SmartRecruiters; no other documents stated</t>
+          <t>CV via Workday portal</t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
@@ -3894,17 +3896,17 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Regulatory Affairs / Quality / Labelling / GxP</t>
+          <t>Clinical operations / clinical research</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Quality Specialist (GxP eQMS: deviations, CAPA, audits)</t>
+          <t>Associate II, TMF Operations (LATAM)</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>ProPharma Group</t>
+          <t>Worldwide Clinical Trials</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -3917,32 +3919,32 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Virtual (remote) - Mexico, Argentina, Brazil</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>unclear</t>
+          <t>remote</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>unclear</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>Location 'India' only; Workday remoteType empty. Footer: 'Whilst ProPharma supports remote working ... we encourage any new hires that are based within a reasonably short commute of one of our offices to work on a hybrid basis'. 'Fluent in English speaking and writing.'</t>
+          <t>'This is a remote role open to candidates based in Latin America.' 'Proficiency in English.' No work-authorisation text seen.</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>Minimum 2 years in a Quality Assurance role; deviation, quality event, CAPA, effectiveness check experience</t>
+          <t>Up to one to two years of relevant TMF experience in CRO or pharma</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>University/bachelor's degree and/or appropriate relevant work experience</t>
+          <t>University degree preferred, ideally life science</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
@@ -3952,7 +3954,7 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>English (fluent)</t>
+          <t>English</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
@@ -3962,42 +3964,43 @@
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t>- Bachelor's degree and/or relevant work experience
-- 2+ years in a QA role
-- Knowledge and experience of GxP Quality Management Systems
-- Deviation, Quality Event, CAPA and effectiveness check experience
-- Fluent English
-- Strong organisation and attention to detail
-- Proficient Microsoft Office</t>
+          <t>- University degree preferred, ideally life science
+- Up to 1-2 years of TMF experience in CRO/pharma
+- Excellent English
+- Data collection, document indexing and naming experience
+- Attention to detail
+- Planning and organisation
+- Word and Excel
+- Familiarity with eTMF systems and clinical research principles</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>- Support and run eQMS activities (change control, deviations, quality events, CAPAs, effectiveness checks)
-- Support client audits and regulatory inspections and track audit CAPA responses
-- Analyse deviations and quality events and report quality KPIs
-- Take part in GxP change management and risk/impact analysis
-- Medical-information-specific: evaluate call and case-report quality against compliance standards</t>
+          <t>- TMF approver and quality-control reviewer activities
+- Process and resolve rejected TMF documents
+- Index and classify essential documents
+- Prepare periodic TMF QC checklists
+- Quality checks against ICH GCP and sponsor expectations</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t>GxP; eQMS; change control; deviations; CAPA; quality events; effectiveness checks; audits and inspections; quality KPIs; root cause</t>
+          <t>TMF quality control; eTMF; essential documents; ICH GCP; document indexing; attention to detail; Excel; English proficiency</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t>GMP/GxP principles, quality management, CAPA and deviation concepts, regulatory inspection awareness.</t>
+          <t>Life-science degree, GCP concepts, document accuracy.</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t>No QA industry experience; work mode and non-resident eligibility not clear from the posting (India listing).</t>
+          <t>No TMF/eTMF experience; must be based in Latin America.</t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t>A bachelor's is enough on education, but 2 years of QA experience in a GxP setting is asked. One clear gap (experience).</t>
+          <t>Degree preference matches, but 1-2 years of TMF experience is asked and the role is open only to candidates based in Latin America.</t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
@@ -4007,12 +4010,12 @@
       </c>
       <c r="X23" s="4" t="inlineStr">
         <is>
-          <t>https://propharmagroup.wd1.myworkdayjobs.com/ppgcareers/job/India/Quality-Specialist_JR10726</t>
+          <t>https://worldwide.wd1.myworkdayjobs.com/External/job/Virtual-Mexico/Associate-II--TMF-Operations_JR102047</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t>Not stated (Workday portal; CV expected)</t>
+          <t>CV via Workday portal</t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
@@ -4046,30 +4049,30 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Clinical operations / clinical research</t>
+          <t>Pharmacovigilance / Drug Safety</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>FSP Clinical Trial Coordinator (Sweden, remote)</t>
+          <t>Drug Safety Associate</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific (PPD clinical research business)</t>
+          <t>Cencora (for Innomar Strategies, Canada)</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G24" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Sweden - Stockholm - Remote</t>
+          <t>Remote, Ontario, Canada</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
@@ -4084,17 +4087,17 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>'Hybrid work if located in Copenhagen or Stockholm... If other location, it will be a remote work setting'; 'proficient local language skills (Swedish or Danish)'; Workday remoteType Fully Remote.</t>
+          <t>'This role is in support of Cencora's patient and provider support and pharma commercialization services in Canada'; 'Bilingual, English/French is an asset'; 'Good internet required for remote work'. No visa or residency wording.</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>0 to 1 year (equivalency considered)</t>
+          <t>'1-3 years experience in Medical Information, Clinical Research or Drug Safety or equivalent and related experience in pharmacy or pharmaceutical fields'</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>High/secondary school diploma plus relevant qualification; bachelor's preferred</t>
+          <t>'Minimum college level education required. A diploma or degree with a concentration in Life Sciences is a strong asset'</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
@@ -4104,7 +4107,7 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>English plus Swedish or Danish</t>
+          <t>English; French an asset</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
@@ -4114,43 +4117,43 @@
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t>- Secondary diploma and relevant qualification; bachelor's preferred
-- About 0-1 year of relevant experience
-- Good English plus proficient Swedish or Danish
-- Working knowledge of ICH GCP and country regulations (to be developed)
-- Good organisational skills and attention to detail
-- Proficient in MS Office
-- Able to learn clinical trial database systems
-- Able to complete the company clinical training programme</t>
+          <t>- College-level education minimum; life sciences degree a strong asset
+- 1-3 years in Medical Information, Clinical Research or Drug Safety (pharmacy experience counts)
+- Knowledge of PV guidelines of Health Canada, US FDA, EMEA and ICH
+- Medical terminology an asset
+- Strong analytical skills
+- Attention to detail and deadlines
+- Office programs
+- Reliable internet for remote work</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>- Administrative and technical support to the project team
-- Support site activation and site lists/feasibility
-- Process documents to (e)TMF and perform TMF reviews
-- Distribute Investigator Site File and pharmacy binder materials
-- Run study metric reconciliation and findings reports</t>
+          <t>- Receive, document and triage adverse events and product quality complaints
+- Request clarification from clients
+- Data entry and submission of AE information into program databases
+- Quality check AE reports and source data verification
+- Screen medical/scientific literature for safety information; prepare reconciliation reports; assist with CAPA</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t>Trial Master File; eTMF; site activation; feasibility; Investigator Site File; ICH GCP; MS Office; attention to detail; organisational skills</t>
+          <t>adverse event information; product quality complaints; triaging; source data verification; screening medical and scientific literature; reconciliation reports; pharmacovigilance guidelines of Health Canada, US FDA, EMEA and ICH; SOP/protocol; non-conformance/CAPA; medical terminology</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t>Degree-level science background, documentation and regulatory awareness, GCP concepts.</t>
+          <t>Adverse event triage, medical terminology, pharmacovigilance guidelines, literature screening, quality checking.</t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t>Swedish or Danish language; no industry experience.</t>
+          <t>1-3 years of experience; Canadian work-authorisation not addressed in the posting; French an asset.</t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t>Experience bar is only 0-1 year and degree preferred, but fluency in Swedish or Danish is required, which is a clear gap unless KT speaks one.</t>
+          <t>Entry-friendly PV intake role that explicitly counts pharmacy experience, but asks for 1-3 years and is based for Canada (likely Canadian work authorisation needed). Closest to a true entry point of the roles found.</t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
@@ -4160,12 +4163,12 @@
       </c>
       <c r="X24" s="4" t="inlineStr">
         <is>
-          <t>https://thermofisher.wd5.myworkdayjobs.com/ThermoFisherCareers/job/Remote-Sweden/FSP-Clinical-Trial-Coordinator_R-01369781</t>
+          <t>https://careers.cencora.com/us/en/hvhapply?jobSeqNo=CHKCENUSR2617957EXTERNALENUS</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t>CV via Workday portal</t>
+          <t>Online application via Cencora careers portal; no other documents stated</t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
@@ -4199,30 +4202,30 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Medical information / medical affairs / medical writing / HEOR &amp; market access</t>
+          <t>Clinical operations / clinical research</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Medical Writer - Medical Information</t>
+          <t>Trial Master File Specialist (TMFS) II</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific (PPD clinical research)</t>
+          <t>Ergomed (PrimeVigilance / Ergomed clinical)</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G25" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Remote, Massachusetts, USA</t>
+          <t>Belgrade, Serbia (the posting also lists Sarajevo / Bosnia and Herzegovina in its structured data)</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -4232,22 +4235,22 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>unclear</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>Location 'Remote, Massachusetts, USA'; pay range given 'based in Massachusetts'. 'Work is performed in an office environment or remotely.' No work-authorisation or residency sentence in the description; US benefits listed ('U.S. colleagues').</t>
+          <t>SmartRecruiters remote flag true; 'Very good English'; no work-authorisation text seen. Title says 'TMF and ALCOA principles experience required'. | Audit correction: Novi Sad is not in the posting. Remote status comes from the employer's flag and page label, not from the description.</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>'Previous experience ... (comparable to 2+ years)'; pharma/CRO experience preferred; scientific writing advantageous</t>
+          <t>TMF maintenance and quality-check experience (ALCOA principles); administrative experience preferably in clinical research</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>Bachelor's degree in a scientific discipline or equivalent; advanced degree preferred</t>
+          <t>Not stated</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
@@ -4257,52 +4260,51 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>English (not stated explicitly)</t>
+          <t>English</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>$100,000.00-$120,000.00 (stated 'for this position based in Massachusetts')</t>
+          <t>not stated</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t>- Bachelor's in a scientific discipline
-- Comparable to 2+ years' relevant experience
-- Solid medical writing, editing and proofreading skills
-- Ability to interpret and present complex data accurately
-- Good knowledge of document management systems, Excel, Outlook
-- Skilled with client templates
-- Pharma/CRO experience preferred</t>
+          <t>- TMF maintenance and quality check experience
+- ALCOA principles knowledge
+- Administrative work experience, preferably in international clinical research
+- Proficiency in Excel
+- Takes responsibility for TMF quality
+- Very good written and spoken English</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>- Medical and scientific writing from planning to final drafts
-- Write routine deliverables such as medical information documents, publications and clinical study documents
-- Work with internal and external clients on communication
-- Follow SOPs, work instructions and quality processes
-- May help with timelines and budgets</t>
+          <t>- Set up and maintain the Trial Master File
+- Process and index project documents per SOPs
+- Quality-check documents under ALCOA+
+- Prepare TMF status reports
+- Support audit preparation and TMF reconciliation at closure</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t>medical and scientific writing; medical information documents; publications; clinical study documents; proofreading; editorial skills; interpret and present complex data; document management systems; attention to detail; SOPs</t>
+          <t>Trial Master File; ALCOA+; document indexing; quality check; TMF reconciliation; audit preparation; Excel</t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t>Scientific literature appraisal, drug-information writing, MPharm dissertation/writing, familiarity with clinical study documents.</t>
+          <t>Data-integrity (ALCOA) concepts, documentation, audit awareness.</t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t>About 2 years of writing/industry experience; probably needs US work authorisation and residence (not stated either way); CRO experience preferred.</t>
+          <t>No TMF experience; Balkan-region location (unclear whether non-residents can apply).</t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t>One clear gap: the posting asks for experience 'comparable to 2+ years' and it is a US-based remote role with a Massachusetts pay scale, with no statement that non-US residents can apply. The writing content (medical information documents, publications) fits an MPharm well.</t>
+          <t>Labelled Entry Level and fully remote, but the title itself says TMF experience is required, which KT lacks.</t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
@@ -4312,12 +4314,12 @@
       </c>
       <c r="X25" s="4" t="inlineStr">
         <is>
-          <t>https://thermofisher.wd5.myworkdayjobs.com/ThermoFisherCareers/job/Remote-Massachusetts-USA/Medical-Writer---Medical-Information_R-01364891-1/apply</t>
+          <t>https://jobs.smartrecruiters.com/Ergomed/744000155752099-trial-master-file-specialist-tmfs-ii-tmf-and-alcoa-principles-experience-required?oga=true</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t>Not stated (Workday portal; CV)</t>
+          <t>Application through SmartRecruiters (CV)</t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
@@ -4351,30 +4353,30 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Clinical operations / clinical research</t>
+          <t>Regulatory Affairs / Quality / Labelling / GxP</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Associate II, TMF Operations (LATAM)</t>
+          <t>Regulatory Information Management Analyst</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Worldwide Clinical Trials</t>
+          <t>Medtronic</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Virtual (remote) - Mexico, Argentina, Brazil</t>
+          <t>Bogota, Colombia</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
@@ -4384,22 +4386,22 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>unclear</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>'This is a remote role open to candidates based in Latin America.' 'Proficiency in English.' No work-authorisation text seen.</t>
+          <t>'This position will work in a remote model in Bogota, supporting global users across multiple regions and time zones. No travel is required.' Workday remoteType = 'Remote'. Language requirement not stated.</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>Up to one to two years of relevant TMF experience in CRO or pharma</t>
+          <t>2 years supporting Regulatory Information Management systems, RA processes or master data management; or a master's degree plus more than 1 year of relevant experience</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>University degree preferred, ideally life science</t>
+          <t>Bachelor's degree in Life Sciences, Public Health, Business or related discipline</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
@@ -4409,7 +4411,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Not stated</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
@@ -4419,43 +4421,41 @@
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t>- University degree preferred, ideally life science
-- Up to 1-2 years of TMF experience in CRO/pharma
-- Excellent English
-- Data collection, document indexing and naming experience
-- Attention to detail
-- Planning and organisation
-- Word and Excel
-- Familiarity with eTMF systems and clinical research principles</t>
+          <t>- Bachelor's degree in life sciences, public health, business or related
+- 2 years in RIM, RA processes or master data management (or master's plus 1+ year)
+- Knowledge of the regulatory affairs lifecycle and submission processes
+- End-user support and issue resolution experience
+- Microsoft Office including Excel
+- Managing several assignments with accuracy</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>- TMF approver and quality-control reviewer activities
-- Process and resolve rejected TMF documents
-- Index and classify essential documents
-- Prepare periodic TMF QC checklists
-- Quality checks against ICH GCP and sponsor expectations</t>
+          <t>- Be point of contact for users of Regulatory Information Management systems
+- Create and maintain submission structures and regulatory records in the RIM environment
+- Build submission assembly templates
+- Data entry, cleansing and master data governance
+- Support the RIM modernisation programme</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t>TMF quality control; eTMF; essential documents; ICH GCP; document indexing; attention to detail; Excel; English proficiency</t>
+          <t>Regulatory Information Management; RIM; regulatory submissions; master data; data quality; regulatory affairs lifecycle; Excel; attention to detail; submission assembly</t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t>Life-science degree, GCP concepts, document accuracy.</t>
+          <t>Regulatory lifecycle knowledge, medicine and product data, documentation accuracy.</t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t>No TMF/eTMF experience; must be based in Latin America.</t>
+          <t>No RIM or master-data experience; role is a Bogota-based remote model and the posting does not say whether non-residents are eligible.</t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t>Degree preference matches, but 1-2 years of TMF experience is asked and the role is open only to candidates based in Latin America.</t>
+          <t>The route 'master's degree plus more than one year of relevant experience' is close to KT's profile if KT has some relevant experience; otherwise the 2-year line is a gap. Colombia-based remote role.</t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="X26" s="4" t="inlineStr">
         <is>
-          <t>https://worldwide.wd1.myworkdayjobs.com/External/job/Virtual-Mexico/Associate-II--TMF-Operations_JR102047</t>
+          <t>https://medtronic.wd1.myworkdayjobs.com/MedtronicCareers/job/Bogot-Bogota-Colombia/IT-Business-Analyst_R70427-1</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t>CV via Workday portal</t>
+          <t>Not stated (Workday portal; CV expected)</t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
@@ -4504,17 +4504,17 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Pharmacovigilance / Drug Safety</t>
+          <t>Healthcare operations / implementation / customer success / clinical product / pharmacy operations</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Drug Safety Associate</t>
+          <t>Patient Support Coordinator (Pharmacy Support team)</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Cencora (for Innomar Strategies, Canada)</t>
+          <t>Montu UK (Alternaleaf / Montu group)</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -4527,32 +4527,32 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>Remote, Ontario, Canada</t>
+          <t>Winnersh Triangle, Berkshire, UK (hybrid: 3 days on site, 2 days home after training)</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>remote</t>
+          <t>hybrid</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>unclear</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>'This role is in support of Cencora's patient and provider support and pharma commercialization services in Canada'; 'Bilingual, English/French is an asset'; 'Good internet required for remote work'. No visa or residency wording.</t>
+          <t>Hybrid from Winnersh Triangle office; weekend working required; shifts 7:30-16:30 or 9:30-18:30. No visa wording on page.</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>'1-3 years experience in Medical Information, Clinical Research or Drug Safety or equivalent and related experience in pharmacy or pharmaceutical fields'</t>
+          <t>Minimum two years' customer service or patient-facing experience; healthcare/pharmacy experience desirable</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>'Minimum college level education required. A diploma or degree with a concentration in Life Sciences is a strong asset'</t>
+          <t>Not stated</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
@@ -4562,53 +4562,50 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>English; French an asset</t>
+          <t>English</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>not stated</t>
+          <t>£28K - £30K (Ashby compensation field)</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t>- College-level education minimum; life sciences degree a strong asset
-- 1-3 years in Medical Information, Clinical Research or Drug Safety (pharmacy experience counts)
-- Knowledge of PV guidelines of Health Canada, US FDA, EMEA and ICH
-- Medical terminology an asset
-- Strong analytical skills
-- Attention to detail and deadlines
-- Office programs
-- Reliable internet for remote work</t>
+          <t>- Two years' experience in customer service or a patient-facing environment
+- Experience handling high volumes of telephone enquiries and difficult conversations
+- Strong attention to detail and accurate record keeping
+- Comfortable using several IT systems
+- Understanding of following SOPs in a regulated environment
+- Desirable: healthcare, pharmacy or other highly regulated experience</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t>- Receive, document and triage adverse events and product quality complaints
-- Request clarification from clients
-- Data entry and submission of AE information into program databases
-- Quality check AE reports and source data verification
-- Screen medical/scientific literature for safety information; prepare reconciliation reports; assist with CAPA</t>
+          <t>- First point of contact for patients on prescriptions, medication availability and deliveries
+- Work with Pharmacy Dispensers on stock and prescription processing queries
+- Escalate clinical questions to qualified healthcare professionals and complex issues to Clinical Governance
+- Keep detailed records of patient interactions to policy and regulatory standards</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t>adverse event information; product quality complaints; triaging; source data verification; screening medical and scientific literature; reconciliation reports; pharmacovigilance guidelines of Health Canada, US FDA, EMEA and ICH; SOP/protocol; non-conformance/CAPA; medical terminology</t>
+          <t>Patient Support; prescription queries; medication availability; telephone enquiries; SOPs; regulated healthcare environment; attention to detail; Pharmacy team; Clinical Governance; patient-facing</t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t>Adverse event triage, medical terminology, pharmacovigilance guidelines, literature screening, quality checking.</t>
+          <t>Medication knowledge, prescription processing, patient communication and escalation of clinical questions.</t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t>1-3 years of experience; Canadian work-authorisation not addressed in the posting; French an asset.</t>
+          <t>Two years' customer service/patient-facing experience may not be evidenced; UK location and weekends; phone-heavy role.</t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t>Entry-friendly PV intake role that explicitly counts pharmacy experience, but asks for 1-3 years and is based for Canada (likely Canadian work authorisation needed). Closest to a true entry point of the roles found.</t>
+          <t>Pharmacy-adjacent patient access/support role at a UK online pharmacy and clinic group. Below MPharm level but a realistic entry point; gaps are the two years of customer-facing experience (pharmacy placements/retail may count) and being based near Winnersh with weekend shifts.</t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
@@ -4618,12 +4615,12 @@
       </c>
       <c r="X27" s="4" t="inlineStr">
         <is>
-          <t>https://careers.cencora.com/us/en/hvhapply?jobSeqNo=CHKCENUSR2617957EXTERNALENUS</t>
+          <t>https://jobs.ashbyhq.com/montu-uk/8f77e50b-133b-4581-9b54-024cc69b722a/application</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t>Online application via Cencora careers portal; no other documents stated</t>
+          <t>Not stated on page (Ashby application form)</t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
@@ -4657,17 +4654,17 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Clinical operations / clinical research</t>
+          <t>Medical information / medical affairs / medical writing / HEOR &amp; market access</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Trial Master File Specialist (TMFS) II</t>
+          <t>Medical Writer - Global Clinical Development</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Ergomed (PrimeVigilance / Ergomed clinical)</t>
+          <t>Regeneron</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -4680,7 +4677,7 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Belgrade, Serbia (same posting also for Novi Sad, Serbia and Sarajevo, Bosnia and Herzegovina); location flag remote=true</t>
+          <t>United States - Remote</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
@@ -4690,22 +4687,22 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>unclear</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>SmartRecruiters remote flag true; 'Very good English'; no work-authorisation text seen. Title says 'TMF and ALCOA principles experience required'.</t>
+          <t>'Location: United States - Remote'; 'Work model: Remote'. Generic notice: 'many roles are required to be performed on-site' and 'background checks ... right to work'. No explicit visa/sponsorship line.</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>TMF maintenance and quality-check experience (ALCOA principles); administrative experience preferably in clinical research</t>
+          <t>1 year of relevant experience</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>Not stated</t>
+          <t>Bachelor's degree; advanced degree preferred</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
@@ -4715,51 +4712,51 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>English (not stated explicitly)</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>not stated</t>
+          <t>$109,900.00 - $179,300.00 (annual, as printed on the posting)</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t>- TMF maintenance and quality check experience
-- ALCOA principles knowledge
-- Administrative work experience, preferably in international clinical research
-- Proficiency in Excel
-- Takes responsibility for TMF quality
-- Very good written and spoken English</t>
+          <t>- Bachelor's degree
+- 1 year of relevant experience
+- Awareness of the clinical research process and applicable regulations/guidelines
+- Scientific and technical reading, writing and editing skills
+- Working knowledge of Word, Acrobat, PowerPoint
+- Familiarity with electronic document management systems
+- Strong organisational and communication skills</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t>- Set up and maintain the Trial Master File
-- Process and index project documents per SOPs
-- Quality-check documents under ALCOA+
-- Prepare TMF status reports
-- Support audit preparation and TMF reconciliation at closure</t>
+          <t>- Develop clinical documents (CSRs, protocols, informed consent forms, narratives, investigator brochures)
+- Manage and facilitate document completion with oversight from Medical Writing leads
+- Run document development meetings and support timelines
+- Synthesise complex discussions into clear written content</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t>Trial Master File; ALCOA+; document indexing; quality check; TMF reconciliation; audit preparation; Excel</t>
+          <t>clinical study reports; protocols; informed consent forms; narratives; investigator brochures; scientific and technical writing; editing; peer-review practices; electronic document management systems; clinical research process</t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t>Data-integrity (ALCOA) concepts, documentation, audit awareness.</t>
+          <t>Scientific writing and referencing from the MPharm, understanding of clinical trials and drug development, GCP awareness if covered in the degree.</t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t>No TMF experience; Balkan-region location (unclear whether non-residents can apply).</t>
+          <t>1 year of relevant (writing/clinical documents) experience; US location/right-to-work likely required.</t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t>Labelled Entry Level and fully remote, but the title itself says TMF experience is required, which KT lacks.</t>
+          <t>Entry bar is low (bachelor's + 1 year), but KT has no industry or regulatory-writing experience yet and the role is US-remote with no statement that non-US residents can apply.</t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
@@ -4769,12 +4766,12 @@
       </c>
       <c r="X28" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/Ergomed/744000155752099-trial-master-file-specialist-tmfs-ii-tmf-and-alcoa-principles-experience-required?oga=true</t>
+          <t>https://regeneron.wd1.myworkdayjobs.com/Careers/job/Remote---United-States/Medical-Writer---Global-Clinical-Development_R51617/apply</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t>Application through SmartRecruiters (CV)</t>
+          <t>Not stated (Workday portal; CV)</t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
@@ -4808,17 +4805,17 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Regulatory Affairs / Quality / Labelling / GxP</t>
+          <t>Clinical operations / clinical research</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Regulatory Information Management Analyst</t>
+          <t>FSP Associate Contract Specialist (site contracts and budgets, Mexico, remote)</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Medtronic</t>
+          <t>Thermo Fisher Scientific (PPD clinical research business)</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -4831,7 +4828,7 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>Bogota, Colombia</t>
+          <t>Mexico - Remote (matching postings exist for Brazil)</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
@@ -4846,17 +4843,17 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>'This position will work in a remote model in Bogota, supporting global users across multiple regions and time zones. No travel is required.' Workday remoteType = 'Remote'. Language requirement not stated.</t>
+          <t>Workday remoteType 'Fully Remote'; 'Effective communication skills (verbal &amp; written) in English and local language'. No work-authorisation text seen.</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>2 years supporting Regulatory Information Management systems, RA processes or master data management; or a master's degree plus more than 1 year of relevant experience</t>
+          <t>0-2 years</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>Bachelor's degree in Life Sciences, Public Health, Business or related discipline</t>
+          <t>Bachelor's degree or equivalent</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
@@ -4866,7 +4863,7 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>Not stated</t>
+          <t>English and local language (Spanish for Mexico)</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
@@ -4876,41 +4873,42 @@
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t>- Bachelor's degree in life sciences, public health, business or related
-- 2 years in RIM, RA processes or master data management (or master's plus 1+ year)
-- Knowledge of the regulatory affairs lifecycle and submission processes
-- End-user support and issue resolution experience
-- Microsoft Office including Excel
-- Managing several assignments with accuracy</t>
+          <t>- Bachelor's degree or equivalent
+- 0-2 years of experience
+- Basic understanding of clinical trial agreements
+- Basic ability to apply principles of investigator grant negotiation
+- General understanding of business and financial principles
+- Strong attention to detail
+- Analytical, decision-based thinking
+- English and local language</t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>- Be point of contact for users of Regulatory Information Management systems
-- Create and maintain submission structures and regulatory records in the RIM environment
-- Build submission assembly templates
-- Data entry, cleansing and master data governance
-- Support the RIM modernisation programme</t>
+          <t>- Draft, review, negotiate and finalise site contract amendments and budgets
+- Negotiate within approved parameters and escalate out-of-parameter issues
+- Coordinate with internal teams so contracts align with site start-up timelines
+- Track and report contracting status</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t>Regulatory Information Management; RIM; regulatory submissions; master data; data quality; regulatory affairs lifecycle; Excel; attention to detail; submission assembly</t>
+          <t>clinical trial agreements; investigator grant; budget negotiation; site start-up; attention to detail; analytical skills; contract tracking</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t>Regulatory lifecycle knowledge, medicine and product data, documentation accuracy.</t>
+          <t>Clinical trial process knowledge from the degree; analytical skills.</t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t>No RIM or master-data experience; role is a Bogota-based remote model and the posting does not say whether non-residents are eligible.</t>
+          <t>No contract/budget negotiation experience; local language; residence in Mexico likely required.</t>
         </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t>The route 'master's degree plus more than one year of relevant experience' is close to KT's profile if KT has some relevant experience; otherwise the 2-year line is a gap. Colombia-based remote role.</t>
+          <t>Posting asks only 0-2 years, but it is a contracts/negotiation role and KT has no contract or finance exposure, which is a clear gap.</t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
@@ -4920,12 +4918,12 @@
       </c>
       <c r="X29" s="4" t="inlineStr">
         <is>
-          <t>https://medtronic.wd1.myworkdayjobs.com/MedtronicCareers/job/Bogot-Bogota-Colombia/IT-Business-Analyst_R70427-1</t>
+          <t>https://thermofisher.wd5.myworkdayjobs.com/ThermoFisherCareers/job/Remote-Mexico/FSP-Associate-Contract-Specialist_R-01371891</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t>Not stated (Workday portal; CV expected)</t>
+          <t>CV via Workday portal</t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
@@ -4964,12 +4962,12 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Patient Support Coordinator (Pharmacy Support team)</t>
+          <t>Associate Consultant - Entry-Level Clinical Data Technology Consulting (London)</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Montu UK (Alternaleaf / Montu group)</t>
+          <t>Veeva Systems</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
@@ -4982,7 +4980,7 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Winnersh Triangle, Berkshire, UK (hybrid: 3 days on site, 2 days home after training)</t>
+          <t>United Kingdom - London</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
@@ -4997,17 +4995,17 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>Hybrid from Winnersh Triangle office; weekend working required; shifts 7:30-16:30 or 9:30-18:30. No visa wording on page.</t>
+          <t>"We require Associate Consultants to live within reasonable commuting distance from Veeva's London office"; "Qualified candidates must be legally authorized to be employed in the United Kingdom. Veeva does not provide sponsorship for employment visa status"</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>Minimum two years' customer service or patient-facing experience; healthcare/pharmacy experience desirable</t>
+          <t>Entry level; 'up to 2 years postgraduate experience maximum'</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>Not stated</t>
+          <t>Bachelor's or Master's in a quantitative or life science field preferred</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
@@ -5017,50 +5015,52 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>English (fluent)</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>£28K - £30K (Ashby compensation field)</t>
+          <t>Starting Annual Salary: 40,000 GBP</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t>- Two years' experience in customer service or a patient-facing environment
-- Experience handling high volumes of telephone enquiries and difficult conversations
-- Strong attention to detail and accurate record keeping
-- Comfortable using several IT systems
-- Understanding of following SOPs in a regulated environment
-- Desirable: healthcare, pharmacy or other highly regulated experience</t>
+          <t>- Bachelor's or Master's degree in a quantitative or life science field is preferred (Pharmacology and Clinical Research are in the list)
+- Open to recent graduates, 'up to 2 years postgraduate experience maximum'
+- Basic familiarity with database concepts, e.g. SQL; Python or R for data manipulation
+- Fluent English, excellent written and verbal communication
+- Willingness to travel up to 20-30% of the time
+- Hybrid: must live within reasonable commuting distance of the office
+- Legal work authorisation required; no visa sponsorship
+- Apply with resume, short cover letter and a quick personality test</t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>- First point of contact for patients on prescriptions, medication availability and deliveries
-- Work with Pharmacy Dispensers on stock and prescription processing queries
-- Escalate clinical questions to qualified healthcare professionals and complex issues to Clinical Governance
-- Keep detailed records of patient interactions to policy and regulatory standards</t>
+          <t>- Lead configuration of the Vault CDMS clinical data platform to each customer's clinical trial requirements
+- Lead discovery workshops with customer stakeholders (Clinical Data Managers, CRCs, CRAs) to gather requirements
+- Scope study requirements, build timeline estimates and keep milestones on track from study design to go-live
+- Guide customers on best practices for clinical data collection and study management</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t>Patient Support; prescription queries; medication availability; telephone enquiries; SOPs; regulated healthcare environment; attention to detail; Pharmacy team; Clinical Governance; patient-facing</t>
+          <t>Clinical Data Management; clinical trial operations; clinical trial data; study workflows; discovery workshops; business requirements; customer-facing; implementation; SQL; data analysis; Clinical Research Associate; design, configure, and deliver</t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t>Medication knowledge, prescription processing, patient communication and escalation of clinical questions.</t>
+          <t>Pharmacology/life-science degree, understanding of clinical trials and drug development, evidence and data handling; this is the 'implement software for clinical trial teams' route into pharma-tech.</t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t>Two years' customer service/patient-facing experience may not be evidenced; UK location and weekends; phone-heavy role.</t>
+          <t>Right to work in the UK and living commutable to London (hybrid). No SQL/Python or software-implementation experience stated in KT's profile. No consulting or CRO experience.</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t>Pharmacy-adjacent patient access/support role at a UK online pharmacy and clinic group. Below MPharm level but a realistic entry point; gaps are the two years of customer-facing experience (pharmacy placements/retail may count) and being based near Winnersh with weekend shifts.</t>
+          <t>Explicitly entry-level, names Pharmacology among preferred degrees and accepts up to 2 years since graduating, which fits a 2024 MPharm. It is B only because of the UK work-authorisation rule, the need to live near the London office and the SQL/Python expectation.</t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="X30" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/montu-uk/8f77e50b-133b-4581-9b54-024cc69b722a/application</t>
+          <t>https://jobs.lever.co/veeva/2f54dda8-9a78-4bfe-89b5-a93a9500db1c/apply</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t>Not stated on page (Ashby application form)</t>
+          <t>Resume, short cover letter, personality test (stated in posting)</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
@@ -5109,17 +5109,17 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Clinical operations / clinical research</t>
+          <t>Healthcare operations / implementation / customer success / clinical product / pharmacy operations</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Site Contract Specialist I</t>
+          <t>Associate Consultant - Entry-Level Clinical Data Technology Consulting (Barcelona)</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>PSI CRO</t>
+          <t>Veeva Systems</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>Mexico City, Mexico - 'Home-based position in Mexico'</t>
+          <t>Spain - Barcelona</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>home-based</t>
+          <t>hybrid</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -5147,17 +5147,17 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>'Home-based position in Mexico. Only CVs in English will be considered.' 'Fluency in Spanish and English, oral and written.'</t>
+          <t>"We require Associate Consultants to live within reasonable commuting distance from Veeva's Barcelona office"; "Qualified candidates must be legally authorized to be employed in the European Union. Veeva does not provide sponsorship for employment visa status"</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>'Previous experience working with study startup operations is required'</t>
+          <t>Entry level; 'up to 2 years postgraduate experience maximum'</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>College/university degree or equivalent combination of education, training and experience</t>
+          <t>Bachelor's or Master's in a quantitative or life science field preferred</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
@@ -5167,52 +5167,52 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>Spanish and English</t>
+          <t>English (fluent); Spanish not mentioned</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>not stated</t>
+          <t>Starting Annual Salary: 37,000 EUR</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t>- University degree or equivalent
-- Previous study start-up operations experience
-- Fluency in Spanish and English
-- Finance/negotiation experience desirable
-- Knowledge of legal documents for clinical trial sites a plus
-- Word, Excel, PowerPoint
-- Works well in a dynamic team</t>
+          <t>- Bachelor's or Master's degree in a quantitative or life science field is preferred (Pharmacology and Clinical Research are in the list)
+- Open to recent graduates, 'up to 2 years postgraduate experience maximum'
+- Basic familiarity with database concepts, e.g. SQL; Python or R for data manipulation
+- Fluent English, excellent written and verbal communication
+- Willingness to travel up to 20-30% of the time
+- Hybrid: must live within reasonable commuting distance of the Barcelona office
+- Legal work authorisation for the EU required; no visa sponsorship
+- Apply with resume, short cover letter and a quick personality test</t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t>- Review and negotiate site budgets
-- Support review and negotiation of clinical trial agreements and investigator grants with PSI Legal
-- Track negotiation status in the CTMS
-- Prepare executable contracts and run signatures
-- File executed contracts in the TMF</t>
+          <t>- Lead configuration of the Vault CDMS clinical data platform to each customer's clinical trial requirements
+- Lead discovery workshops with customer stakeholders (Clinical Data Managers, CRCs, CRAs) to gather requirements
+- Scope study requirements, build timeline estimates and keep milestones on track from study design to go-live
+- Guide customers on best practices for clinical data collection and study management</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t>site budgets; clinical trial agreements; investigator grants; CTMS; Trial Master File; study start-up; contract negotiation</t>
+          <t>Clinical Data Management; clinical trial operations; clinical trial data; study workflows; discovery workshops; business requirements; customer-facing; implementation; SQL; data analysis; Clinical Research Associate; design, configure, and deliver</t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t>Clinical trial process knowledge, documentation.</t>
+          <t>Pharmacology/life-science degree, clinical trial and drug development knowledge, data handling.</t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t>No start-up experience; Spanish; Mexico location.</t>
+          <t>EU right to work and residence near Barcelona. No SQL/Python or implementation experience stated.</t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t>Entry Level label, but the text requires prior study start-up experience, Spanish fluency and a Mexico base.</t>
+          <t>Same programme as the London record; the EU work-authorisation rule and living near Barcelona are the clear gaps. Posted as a separate record because the authorisation rule (EU vs UK) is what decides whether KT can apply.</t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
@@ -5222,12 +5222,12 @@
       </c>
       <c r="X31" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/PSICRO/744000155843309-site-contract-specialist-i-?oga=true</t>
+          <t>https://jobs.lever.co/veeva/4d69a90b-fff2-419c-9ae0-938226dca26c/apply</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t>CV in English via SmartRecruiters</t>
+          <t>Resume, short cover letter, personality test (stated in posting)</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
@@ -5261,17 +5261,17 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Medical information / medical affairs / medical writing / HEOR &amp; market access</t>
+          <t>Clinical operations / clinical research</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Medical Writer - Global Clinical Development</t>
+          <t>Clinical Trials Associate</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Regeneron</t>
+          <t>Worldwide Clinical Trials</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>United States - Remote</t>
+          <t>Virtual (remote), Australia</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
@@ -5299,17 +5299,17 @@
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>'Location: United States - Remote'; 'Work model: Remote'. Generic notice: 'many roles are required to be performed on-site' and 'background checks ... right to work'. No explicit visa/sponsorship line.</t>
+          <t>'This is a REMOTE role open to candidates based in Australia.' 'Proficiency in English.'</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>1 year of relevant experience</t>
+          <t>Minimum one year in a related role</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>Bachelor's degree; advanced degree preferred</t>
+          <t>Degree-level qualification or equivalent experience</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
@@ -5319,51 +5319,52 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>English (not stated explicitly)</t>
+          <t>English</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>$109,900.00 - $179,300.00 (annual, as printed on the posting)</t>
+          <t>not stated</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t>- Bachelor's degree
-- 1 year of relevant experience
-- Awareness of the clinical research process and applicable regulations/guidelines
-- Scientific and technical reading, writing and editing skills
-- Working knowledge of Word, Acrobat, PowerPoint
-- Familiarity with electronic document management systems
-- Strong organisational and communication skills</t>
+          <t>- Degree-level qualification or equivalent
+- At least 1 year in a related role
+- Excellent English
+- Advanced Microsoft Office
+- Working knowledge of ICH, GCP and FDA/EU requirements
+- Organisation and multitasking
+- Attention to detail</t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>- Develop clinical documents (CSRs, protocols, informed consent forms, narratives, investigator brochures)
-- Manage and facilitate document completion with oversight from Medical Writing leads
-- Run document development meetings and support timelines
-- Synthesise complex discussions into clear written content</t>
+          <t>- Coordinate and track system access for project team members
+- Maintain project portals with quality checks
+- Prepare and ship Investigator Site File documentation
+- Submit documents to the Trial Master File
+- Prepare meeting minutes and track training</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t>clinical study reports; protocols; informed consent forms; narratives; investigator brochures; scientific and technical writing; editing; peer-review practices; electronic document management systems; clinical research process</t>
+          <t>Investigator Site File; Trial Master File; ICH GCP; meeting minutes; document version control; Microsoft Office; attention to detail</t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t>Scientific writing and referencing from the MPharm, understanding of clinical trials and drug development, GCP awareness if covered in the degree.</t>
+          <t>Degree, GCP/regulatory awareness, documentation.</t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t>1 year of relevant (writing/clinical documents) experience; US location/right-to-work likely required.</t>
+          <t>One year of related experience; must be Australia-based.</t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t>Entry bar is low (bachelor's + 1 year), but KT has no industry or regulatory-writing experience yet and the role is US-remote with no statement that non-US residents can apply.</t>
+          <t>Genuine CTA role with a one-year-experience bar; open only to Australia-based candidates.</t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
@@ -5373,12 +5374,12 @@
       </c>
       <c r="X32" s="4" t="inlineStr">
         <is>
-          <t>https://regeneron.wd1.myworkdayjobs.com/Careers/job/Remote---United-States/Medical-Writer---Global-Clinical-Development_R51617/apply</t>
+          <t>https://worldwide.wd1.myworkdayjobs.com/External/job/Sydney-Australia/Clinical-Trials-Associate_JR103200</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t>Not stated (Workday portal; CV)</t>
+          <t>CV via Workday portal</t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
@@ -5412,35 +5413,35 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Clinical operations / clinical research</t>
+          <t>Medical information / medical affairs / medical writing / HEOR &amp; market access</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>FSP Associate Contract Specialist (site contracts and budgets, Mexico, remote)</t>
+          <t>Associate, Market Access Consulting (Brazil)</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific (PPD clinical research business)</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G33" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>Mexico - Remote (matching postings exist for Brazil)</t>
+          <t>Sao Paulo, Brazil</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>remote</t>
+          <t>unclear</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -5450,17 +5451,17 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>Workday remoteType 'Fully Remote'; 'Effective communication skills (verbal &amp; written) in English and local language'. No work-authorisation text seen.</t>
+          <t>'A strong academic record (GPA 3.5/4 or greater) with a Bachelors or Master's Degree, preferable in ... Biology, biochemistry, economics, ... public health ...'; 'Excellent conversational and business English'; 'Please submit your resume in English. Other languages will not be considered.'; 'willingness to travel as needed (&lt;10% on average)'. Work mode not stated.</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>0-2 years</t>
+          <t>No years stated</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>Bachelor's degree or equivalent</t>
+          <t>Bachelor's or Master's, strong academic record (GPA 3.5/4 or greater)</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
@@ -5470,7 +5471,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>English and local language (Spanish for Mexico)</t>
+          <t>Business English; resume must be in English (Portuguese not mentioned)</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
@@ -5480,42 +5481,40 @@
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t>- Bachelor's degree or equivalent
-- 0-2 years of experience
-- Basic understanding of clinical trial agreements
-- Basic ability to apply principles of investigator grant negotiation
-- General understanding of business and financial principles
-- Strong attention to detail
-- Analytical, decision-based thinking
-- English and local language</t>
+          <t>- GPA 3.5/4 or greater
+- Bachelor's or Master's (biology, economics, public health etc.)
+- Excellent conversational and business English
+- Basic SQL and Office suite
+- Interest in the healthcare industry
+- Project and time management</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>- Draft, review, negotiate and finalise site contract amendments and budgets
-- Negotiate within approved parameters and escalate out-of-parameter issues
-- Coordinate with internal teams so contracts align with site start-up timelines
-- Track and report contracting status</t>
+          <t>- Run quantitative analytics for Market Access strategy consulting using big-data assets
+- Conduct primary and secondary research on markets, payers, physicians, patients and competitors
+- Build predictive models for contracting, affordability programmes and brand performance
+- Turn analyses into client reports and presentations</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t>clinical trial agreements; investigator grant; budget negotiation; site start-up; attention to detail; analytical skills; contract tracking</t>
+          <t>market access; payers; quantitative analytics; secondary research; SQL; Office suite; healthcare industry; project management; QC standards; English</t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t>Clinical trial process knowledge from the degree; analytical skills.</t>
+          <t>Healthcare-system knowledge, pharmacoeconomics module, interest in access to medicines.</t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t>No contract/budget negotiation experience; local language; residence in Mexico likely required.</t>
+          <t>Needs a 3.5/4 GPA equivalent (check MPharm grade); basic SQL; Brazil location and unknown remote option.</t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t>Posting asks only 0-2 years, but it is a contracts/negotiation role and KT has no contract or finance exposure, which is a clear gap.</t>
+          <t>No experience is required and any science degree is accepted, but a GPA of 3.5/4 or greater is demanded, the work is quantitative consulting rather than medical information, and it sits in Sao Paulo with no stated remote option.</t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
@@ -5525,12 +5524,12 @@
       </c>
       <c r="X33" s="4" t="inlineStr">
         <is>
-          <t>https://thermofisher.wd5.myworkdayjobs.com/ThermoFisherCareers/job/Remote-Mexico/FSP-Associate-Contract-Specialist_R-01371891</t>
+          <t>https://iqvia.wd1.myworkdayjobs.com/IQVIA/job/So-Paulo-Brazil/Associate--Market-Access-Consulting--Brazil-_R1567454/apply</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t>CV via Workday portal</t>
+          <t>Resume in English (as stated)</t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
@@ -5564,35 +5563,35 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Healthcare operations / implementation / customer success / clinical product / pharmacy operations</t>
+          <t>Pharmacovigilance / Drug Safety</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Associate Consultant - Entry-Level Clinical Data Technology Consulting (London)</t>
+          <t>Safety Committee Administrator</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Veeva Systems</t>
+          <t>Thermo Fisher Scientific (PPD clinical research)</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>United Kingdom - London</t>
+          <t>Remote, North Carolina, USA</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>hybrid</t>
+          <t>remote</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
@@ -5602,17 +5601,17 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>"We require Associate Consultants to live within reasonable commuting distance from Veeva's London office"; "Qualified candidates must be legally authorized to be employed in the United Kingdom. Veeva does not provide sponsorship for employment visa status"</t>
+          <t>Location 'Remote, North Carolina, USA'; no explicit work-authorisation wording on the page, so a US location is implied.</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>Entry level; 'up to 2 years postgraduate experience maximum'</t>
+          <t>'comparable to at least 2 years'</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>Bachelor's or Master's in a quantitative or life science field preferred</t>
+          <t>High / secondary school diploma or equivalent and relevant formal academic / vocational qualification</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
@@ -5622,52 +5621,51 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>English (fluent)</t>
+          <t>English</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>Starting Annual Salary: 40,000 GBP</t>
+          <t>not stated</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t>- Bachelor's or Master's degree in a quantitative or life science field is preferred (Pharmacology and Clinical Research are in the list)
-- Open to recent graduates, 'up to 2 years postgraduate experience maximum'
-- Basic familiarity with database concepts, e.g. SQL; Python or R for data manipulation
-- Fluent English, excellent written and verbal communication
-- Willingness to travel up to 20-30% of the time
-- Hybrid: must live within reasonable commuting distance of the office
-- Legal work authorisation required; no visa sponsorship
-- Apply with resume, short cover letter and a quick personality test</t>
+          <t>- Secondary school diploma or equivalent
+- Experience comparable to at least 2 years
+- Excellent MS Office skills
+- Communication and liaison skills with clients and project teams
+- Attention to detail and accuracy
+- Ability to prioritise under strict deadlines</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>- Lead configuration of the Vault CDMS clinical data platform to each customer's clinical trial requirements
-- Lead discovery workshops with customer stakeholders (Clinical Data Managers, CRCs, CRAs) to gather requirements
-- Scope study requirements, build timeline estimates and keep milestones on track from study design to go-live
-- Guide customers on best practices for clinical data collection and study management</t>
+          <t>- Set up and administer Data and Safety Monitoring Board / Endpoint Adjudication Committee services
+- Track member contracts and honoraria
+- Attend meetings and write minutes
+- Compile adjudication dossiers
+- Keep PV files audit-ready</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t>Clinical Data Management; clinical trial operations; clinical trial data; study workflows; discovery workshops; business requirements; customer-facing; implementation; SQL; data analysis; Clinical Research Associate; design, configure, and deliver</t>
+          <t>Data and Safety Monitoring Boards (DSMB); Endpoint Adjudication Committees (EAC); meeting minutes; adjudication dossiers; audit ready; contract tracking</t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t>Pharmacology/life-science degree, understanding of clinical trials and drug development, evidence and data handling; this is the 'implement software for clinical trial teams' route into pharma-tech.</t>
+          <t>Understanding of clinical trial safety oversight (DSMB) from pharmacy and clinical trials teaching.</t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t>Right to work in the UK and living commutable to London (hybrid). No SQL/Python or software-implementation experience stated in KT's profile. No consulting or CRO experience.</t>
+          <t>About 2 years of experience; US location; administrative rather than clinical content.</t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t>Explicitly entry-level, names Pharmacology among preferred degrees and accepts up to 2 years since graduating, which fits a 2024 MPharm. It is B only because of the UK work-authorisation rule, the need to live near the London office and the SQL/Python expectation.</t>
+          <t>Safety-committee administration role open to non-degree applicants but asking for about 2 years' experience; US-based remote, so mainly feasible only with US work rights.</t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
@@ -5677,12 +5675,12 @@
       </c>
       <c r="X34" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/veeva/2f54dda8-9a78-4bfe-89b5-a93a9500db1c/apply</t>
+          <t>https://thermofisher.wd5.myworkdayjobs.com/ThermoFisherCareers/job/Remote-North-Carolina-USA/Safety-Committee-Administrator_R-01370230</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t>Resume, short cover letter, personality test (stated in posting)</t>
+          <t>Workday portal application; no other documents stated</t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
@@ -5716,30 +5714,30 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Healthcare operations / implementation / customer success / clinical product / pharmacy operations</t>
+          <t>Medical information / medical affairs / medical writing / HEOR &amp; market access</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Associate Consultant - Entry-Level Clinical Data Technology Consulting (Barcelona)</t>
+          <t>Research Associate, MedTech Reimbursement &amp; Market Access (RHEMA)</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Veeva Systems</t>
+          <t>IQVIA MedTech (MCRA)</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G35" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>Spain - Barcelona</t>
+          <t>Washington, DC, United States</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
@@ -5754,17 +5752,17 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>"We require Associate Consultants to live within reasonable commuting distance from Veeva's Barcelona office"; "Qualified candidates must be legally authorized to be employed in the European Union. Veeva does not provide sponsorship for employment visa status"</t>
+          <t>'This position is hybrid out of our Washington, DC office.' Degrees accepted: 'health economics, public health, health policy, epidemiology, economics, statistics, life sciences, or a related discipline'. No visa statement.</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>Entry level; 'up to 2 years postgraduate experience maximum'</t>
+          <t>No years required; prior internship/academic/consulting/CRO/health-plan experience preferred</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>Bachelor's or Master's in a quantitative or life science field preferred</t>
+          <t>Bachelor's in health economics, public health, health policy, epidemiology, economics, statistics, life sciences or related; advanced degree preferred but not required</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
@@ -5774,52 +5772,51 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>English (fluent); Spanish not mentioned</t>
+          <t>English</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>Starting Annual Salary: 37,000 EUR</t>
+          <t>$58,700.00 - $146,800.00 (annualised base pay range printed on the posting)</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t>- Bachelor's or Master's degree in a quantitative or life science field is preferred (Pharmacology and Clinical Research are in the list)
-- Open to recent graduates, 'up to 2 years postgraduate experience maximum'
-- Basic familiarity with database concepts, e.g. SQL; Python or R for data manipulation
-- Fluent English, excellent written and verbal communication
-- Willingness to travel up to 20-30% of the time
-- Hybrid: must live within reasonable commuting distance of the Barcelona office
-- Legal work authorisation for the EU required; no visa sponsorship
-- Apply with resume, short cover letter and a quick personality test</t>
+          <t>- Bachelor's in a related discipline (life sciences accepted)
+- Strong research, analytical, quantitative and writing skills
+- Familiarity with literature review, real-world evidence, health economics, PROs, publication research
+- Ability to organise multiple assignments and meet deadlines
+- Excellent written and oral communication
+- Word, PowerPoint and Excel proficiency</t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t>- Lead configuration of the Vault CDMS clinical data platform to each customer's clinical trial requirements
-- Lead discovery workshops with customer stakeholders (Clinical Data Managers, CRCs, CRAs) to gather requirements
-- Scope study requirements, build timeline estimates and keep milestones on track from study design to go-live
-- Guide customers on best practices for clinical data collection and study management</t>
+          <t>- Research Medicare/Medicaid/payer coverage, coding and payment policy
+- Run systematic and targeted literature searches and evidence-gap assessments
+- Support HEOR, burden-of-illness and budget-impact analyses under a project lead
+- Support publication planning, evidence-generation plans and value tools
+- Prepare Word/PowerPoint/Excel deliverables and present findings</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t>Clinical Data Management; clinical trial operations; clinical trial data; study workflows; discovery workshops; business requirements; customer-facing; implementation; SQL; data analysis; Clinical Research Associate; design, configure, and deliver</t>
+          <t>literature searches; evidence landscape reviews; evidence-gap assessments; real-world evidence; health economics and outcomes research; burden-of-illness analyses; publication planning; payer; Word, PowerPoint and Excel; reimbursement</t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t>Pharmacology/life-science degree, clinical trial and drug development knowledge, data handling.</t>
+          <t>Literature searching, evidence appraisal, pharmacoeconomics module content, healthcare-system knowledge.</t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t>EU right to work and residence near Barcelona. No SQL/Python or implementation experience stated.</t>
+          <t>US location/work authorisation; US payer-policy knowledge (Medicare/Medicaid); the posting shows no sponsorship statement.</t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t>Same programme as the London record; the EU work-authorisation rule and living near Barcelona are the clear gaps. Posted as a separate record because the authorisation rule (EU vs UK) is what decides whether KT can apply.</t>
+          <t>Qualifications are within reach (life-science degree, no years required), but it is a hybrid Washington DC role for a US healthcare-policy audience, so KT would need US work authorisation and relocation.</t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
@@ -5829,12 +5826,12 @@
       </c>
       <c r="X35" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/veeva/4d69a90b-fff2-419c-9ae0-938226dca26c/apply</t>
+          <t>https://iqvia.wd1.myworkdayjobs.com/IQVIA/job/Washington-DC-United-States-of-America/Research-Associate--Reimbursement--Health-Economics---Market-Access_R1572565/apply</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t>Resume, short cover letter, personality test (stated in posting)</t>
+          <t>Not stated (Workday portal; CV)</t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
@@ -5868,55 +5865,55 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Clinical operations / clinical research</t>
+          <t>Medical information / medical affairs / medical writing / HEOR &amp; market access</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Clinical Trials Associate</t>
+          <t>Medical Information Associate</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Worldwide Clinical Trials</t>
+          <t>Novartis</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Virtual (remote), Australia</t>
+          <t>Seoul (South Korea)</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>remote</t>
+          <t>unclear</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>unclear</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>'This is a REMOTE role open to candidates based in Australia.' 'Proficiency in English.'</t>
+          <t>Location: Seoul. 'Bachelor's degree in Life Sciences or a relevant healthcare discipline, such as pharmacy, nursing or medicine.' 'Excellent customer service, communication, English reading and writing skills.' Work mode not stated; the role works 'in line with local regulations', so a Korean-market role. Korean is not mentioned in the text. | Application end date: 2026-10-31 (added after audit).</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>Minimum one year in a related role</t>
+          <t>At least one year of experience in a healthcare setting</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>Degree-level qualification or equivalent experience</t>
+          <t>Bachelor's in life sciences or healthcare discipline (pharmacy accepted)</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
@@ -5926,7 +5923,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>English reading/writing; Korean not mentioned but the market is Korea</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
@@ -5936,42 +5933,42 @@
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t>- Degree-level qualification or equivalent
-- At least 1 year in a related role
-- Excellent English
-- Advanced Microsoft Office
-- Working knowledge of ICH, GCP and FDA/EU requirements
-- Organisation and multitasking
-- Attention to detail</t>
+          <t>- Bachelor's in life sciences/pharmacy/nursing/medicine
+- At least 1 year of experience in a healthcare setting
+- Strong scientific and medical knowledge
+- Proficiency in databases/systems used for medical information
+- Excellent customer service and communication
+- Detail-oriented, compliance-minded</t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t>- Coordinate and track system access for project team members
-- Maintain project portals with quality checks
-- Prepare and ship Investigator Site File documentation
-- Submit documents to the Trial Master File
-- Prepare meeting minutes and track training</t>
+          <t>- Answer unsolicited medical enquiries accurately and on time
+- Develop and maintain medical information responses from approved data and current evidence
+- Run literature searches and critically evaluate data
+- Document enquiries and rationale in medical information systems
+- Review promotional/non-promotional content for scientific accuracy
+- Share aggregated insights on recurring questions and evidence gaps</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t>Investigator Site File; Trial Master File; ICH GCP; meeting minutes; document version control; Microsoft Office; attention to detail</t>
+          <t>unsolicited medical enquiries; non-promotional; literature searches; critically evaluate scientific data; medical information systems; scientific accuracy; approved scientific data; healthcare setting; customer service; compliance</t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t>Degree, GCP/regulatory awareness, documentation.</t>
+          <t>Drug information, literature evaluation, evidence appraisal, regulatory awareness.</t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t>One year of related experience; must be Australia-based.</t>
+          <t>1 year healthcare-setting experience; Seoul location; Korean language probably needed in practice (not stated).</t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t>Genuine CTA role with a one-year-experience bar; open only to Australia-based candidates.</t>
+          <t>Pharmacy is named as an accepted degree and the duties are classic medical information; the gap is 1 year in a healthcare setting (MPharm placements may count) and the Seoul location with probable Korean-language need.</t>
         </is>
       </c>
       <c r="W36" s="3" t="inlineStr">
@@ -5981,12 +5978,12 @@
       </c>
       <c r="X36" s="4" t="inlineStr">
         <is>
-          <t>https://worldwide.wd1.myworkdayjobs.com/External/job/Sydney-Australia/Clinical-Trials-Associate_JR103200</t>
+          <t>https://novartis.wd3.myworkdayjobs.com/Novartis_Careers/job/Seoul/Medical-Information-Associate_REQ-10087203/apply</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t>CV via Workday portal</t>
+          <t>Not stated (Workday portal; CV)</t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
@@ -6020,55 +6017,55 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Medical information / medical affairs / medical writing / HEOR &amp; market access</t>
+          <t>Regulatory Affairs / Quality / Labelling / GxP</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Associate, Market Access Consulting (Brazil)</t>
+          <t>Quality and Compliance Assistant</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>IQVIA</t>
+          <t>Labcorp</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G37" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>Sao Paulo, Brazil</t>
+          <t>Bengaluru, India</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
+          <t>remote</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
           <t>unclear</t>
         </is>
       </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>unclear</t>
-        </is>
-      </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>'A strong academic record (GPA 3.5/4 or greater) with a Bachelors or Master's Degree, preferable in ... Biology, biochemistry, economics, ... public health ...'; 'Excellent conversational and business English'; 'Please submit your resume in English. Other languages will not be considered.'; 'willingness to travel as needed (&lt;10% on average)'. Work mode not stated.</t>
+          <t>'Labcorp is seeking a remote Quality and Compliance Assistant'; 'Remote based'; schedule 'Monday - Friday, 2PM - 11PM'. No work-authorisation wording; location Bengaluru, India.</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>No years stated</t>
+          <t>1 year of experience in the job discipline</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>Bachelor's or Master's, strong academic record (GPA 3.5/4 or greater)</t>
+          <t>Master's degree in life sciences (preferred: associate degree level of laboratory or animal technician, biological sciences, pharmacy or medical nurse, or equivalent)</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
@@ -6078,7 +6075,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>Business English; resume must be in English (Portuguese not mentioned)</t>
+          <t>Good English speaking, writing and reading</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
@@ -6088,40 +6085,41 @@
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t>- GPA 3.5/4 or greater
-- Bachelor's or Master's (biology, economics, public health etc.)
-- Excellent conversational and business English
-- Basic SQL and Office suite
-- Interest in the healthcare industry
-- Project and time management</t>
+          <t>- Master's degree in life sciences
+- 1 year of experience in the job discipline
+- Good English communication
+- Time management
+- MS Office user knowledge
+- Attention to detail</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t>- Run quantitative analytics for Market Access strategy consulting using big-data assets
-- Conduct primary and secondary research on markets, payers, physicians, patients and competitors
-- Build predictive models for contracting, affordability programmes and brand performance
-- Turn analyses into client reports and presentations</t>
+          <t>- Administrative tasks for the Quality and Compliance group
+- Support metric collation
+- Learn Veeva Quality Systems
+- Assist in Customer Hallmark Health Check discussions
+- Work under regular supervision</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t>market access; payers; quantitative analytics; secondary research; SQL; Office suite; healthcare industry; project management; QC standards; English</t>
+          <t>Quality and Compliance; Veeva Quality Systems; metrics; attention to detail; time management; MS Office; Master's degree in life sciences</t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t>Healthcare-system knowledge, pharmacoeconomics module, interest in access to medicines.</t>
+          <t>GxP and quality system awareness, document control concepts.</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t>Needs a 3.5/4 GPA equivalent (check MPharm grade); basic SQL; Brazil location and unknown remote option.</t>
+          <t>No year of industry quality experience; role is tied to India time zone and posting does not say whether non-residents can apply.</t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t>No experience is required and any science degree is accepted, but a GPA of 3.5/4 or greater is demanded, the work is quantitative consulting rather than medical information, and it sits in Sao Paulo with no stated remote option.</t>
+          <t>KT meets the master's-level education line, but one year in the discipline is asked and the schedule is a late-day shift (2PM-11PM) in India. Administrative entry role in a GxP quality group.</t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
@@ -6131,12 +6129,12 @@
       </c>
       <c r="X37" s="4" t="inlineStr">
         <is>
-          <t>https://iqvia.wd1.myworkdayjobs.com/IQVIA/job/So-Paulo-Brazil/Associate--Market-Access-Consulting--Brazil-_R1567454/apply</t>
+          <t>https://labcorp.wd1.myworkdayjobs.com/External/job/Bengaluru-India/Quality-and-Compliance-Assistant_2633009</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t>Resume in English (as stated)</t>
+          <t>Not stated (Workday portal; CV expected)</t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
@@ -6170,35 +6168,35 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Healthcare operations / implementation / customer success / clinical product / pharmacy operations</t>
+          <t>Pharmacovigilance / Drug Safety</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Quality Assurance Officer (Leafio pharmaceutical wholesale)</t>
+          <t>Senior Pharmacovigilance Associate (ICSR management; Kraków, remote; same title also posted for Cluj-Napoca, Romania)</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Montu UK (Leafio)</t>
+          <t>PrimeVigilance (Ergomed Group)</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G38" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Winnersh, Berkshire, UK (hybrid)</t>
+          <t>Kraków, Poland (remote flag). Also: Cluj-Napoca, Romania, remote flag, https://jobs.smartrecruiters.com/Ergomed/744000154954939-senior-pharmacovigilance-associate (posted 2026-10-12); Bucharest is hybrid</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>hybrid</t>
+          <t>remote</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
@@ -6208,17 +6206,17 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>Hybrid Winnersh; work-from-home options mentioned; no visa wording. Needs UK GDP/MHRA experience.</t>
+          <t>Location tied to Poland/Romania; 'English - advanced (spoken, written)'; role includes acting as LCPPV and PRLS for the specified country and language 'as agreed with the line manager'. No visa wording.</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>More than 2 years in a GMDP-regulated pharmaceutical environment</t>
+          <t>'Minimum 1 year of work experience in pharmacovigilance'</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>Not stated</t>
+          <t>'Life science graduate, pharmacy, nursing, other healthcare related qualification or experience in pharmacovigilance'</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
@@ -6228,49 +6226,51 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>English advanced (spoken and written); local-language duties may apply</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>£50K - £55K (Ashby compensation field)</t>
+          <t>not stated</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t>- Knowledge of GMP or GDP and the pharmaceutical wholesale regulatory framework
-- More than 2 years' experience in a GMDP-regulated environment
-- Experience with Quality Management Systems: complaints, CAPAs, deviations, risk management, change control, audits
-- Experience with unlicensed products under Regulation 167
-- Strong report writing and attention to detail</t>
+          <t>- Life science / pharmacy / nursing graduate or PV experience
+- Minimum 1 year of PV work experience
+- Advanced English
+- Organisation skills and attention to detail
+- Time and issue management
+- Advanced MS Office literacy</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t>- Keep deviations, change controls, risk assessments and CAPAs on time
-- Maintain the QMS: SOPs, policies, document control, training records
-- Support batch traceability, CoA documentation and batch release checks
-- Support complaints, audits and MHRA inspections and the Responsible Person</t>
+          <t>- Process ICSRs from all sources to regulations and client timelines; ICSR follow-up
+- SAE/SUSAR management incl. reconciliation, protocol and Safety Management Plan review
+- Product quality complaint handling and medical information interaction
+- MedDRA and WHO coding
+- Database outputs and monthly client reports; may act as LCPPV/PRLS for a country</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t>Good Distribution Practice; GDP; QMS; CAPA; deviations; change control; Regulation 167; MHRA; SOPs; document control; complaints; audits</t>
+          <t>Individual Case Safety Reports (ICSRs); ICSR follow up; SAE/SUSAR Management; reconciliation; Product Quality Complaint handling; MedDRA and WHO coding; Safety Management Plan; personal data protection; Local Contact Person for Pharmacovigilance (LCPPV)</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t>GDP/GMP awareness, medicines regulation (MHRA), pharmaceutical quality systems.</t>
+          <t>Pharmacy degree is named; MedDRA/WHO drug coding, ADR assessment, quality complaints and regulatory reporting map onto MPharm content.</t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t>More than 2 years GMDP experience; Reg 167 unlicensed-products experience; UK location.</t>
+          <t>Minimum 1 year PV experience; Poland/Romania residency likely needed; possible local language duties.</t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t>Pharmaceutical wholesale quality role where an MPharm background is relevant; it asks for more than 2 years in a GMDP environment, which is the main gap, so this is a stretch rather than a fit. Quality/regulatory roles are covered more fully by other role families.</t>
+          <t>Pharmacy graduate is an accepted background and the role is tagged Entry Level on the ATS, but it asks for at least 1 year of PV work experience despite the 'Senior' title. Location is tied to Poland/Romania.</t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="X38" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/montu-uk/d3f2d04d-1b78-45cf-8886-1525a0d92c62/application</t>
+          <t>https://jobs.smartrecruiters.com/Ergomed/744000154955029-senior-pharmacovigilance-associate?oga=true</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t>Not stated on page (Ashby application form)</t>
+          <t>Online application on SmartRecruiters; no other documents stated</t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
@@ -6319,55 +6319,55 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Pharmacovigilance / Drug Safety</t>
+          <t>Healthcare operations / implementation / customer success / clinical product / pharmacy operations</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Safety Committee Administrator</t>
+          <t>Project Delivery Specialist</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific (PPD clinical research)</t>
+          <t>Tandem Health</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G39" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>Remote, North Carolina, USA</t>
+          <t>London (on site; frequent customer-site travel across the UK, occasional trips to Stockholm)</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>remote</t>
+          <t>on-site</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>unclear</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>Location 'Remote, North Carolina, USA'; no explicit work-authorisation wording on the page, so a US location is implied.</t>
+          <t>No visa or residency wording. 'Ashby workplaceType = OnSite'; London office working day is part of the interview process; 'frequent trips to customer sites across the UK'</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>'comparable to at least 2 years'</t>
+          <t>'You've delivered rollouts before' in delivery, project, implementation or customer onboarding roles; 'ideal for somebody early in their career'</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>High / secondary school diploma or equivalent and relevant formal academic / vocational qualification</t>
+          <t>Not stated</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
@@ -6377,7 +6377,7 @@
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>English (CV in English)</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
@@ -6387,41 +6387,42 @@
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t>- Secondary school diploma or equivalent
-- Experience comparable to at least 2 years
-- Excellent MS Office skills
-- Communication and liaison skills with clients and project teams
-- Attention to detail and accuracy
-- Ability to prioritise under strict deadlines</t>
+          <t>- Has delivered rollouts before in delivery/project/implementation/customer-onboarding roles
+- Comfortable with implementation plans, governance, RAID logs, dependencies and reporting
+- Experience of NHS and/or private healthcare environments is 'ideally' wanted
+- Confident with senior and frontline stakeholders
+- Willing to travel frequently to UK customer sites
+- Nice to have: digital health/SaaS implementations in regulated settings
+- Nice to have: NHS governance/IG (DPIA, DCB standards, DTAC)</t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t>- Set up and administer Data and Safety Monitoring Board / Endpoint Adjudication Committee services
-- Track member contracts and honoraria
-- Attend meetings and write minutes
-- Compile adjudication dossiers
-- Keep PV files audit-ready</t>
+          <t>- Run several implementations in parallel with 60-90 day plans from kickoff to go-live
+- Keep customer clinical, ops and IT leads aligned with Medical Ops, Product, Engineering and Commercial
+- Spot risks early and unblock issues
+- Coordinate training, comms and support readiness and track adoption after go-live
+- Build repeatable delivery playbooks and templates</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t>Data and Safety Monitoring Boards (DSMB); Endpoint Adjudication Committees (EAC); meeting minutes; adjudication dossiers; audit ready; contract tracking</t>
+          <t>implementation plans; go-live; rollout; stakeholders; RAID; dependencies; adoption; playbooks; NHS; digital health; regulated; customer onboarding</t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t>Understanding of clinical trial safety oversight (DSMB) from pharmacy and clinical trials teaching.</t>
+          <t>Understanding of clinical settings and NHS medicines governance; pharmacy placements give exposure to how clinicians and IT interact.</t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t>About 2 years of experience; US location; administrative rather than clinical content.</t>
+          <t>No stated implementation/project delivery experience. On-site in London. Right to work not stated but implied UK.</t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t>Safety-committee administration role open to non-degree applicants but asking for about 2 years' experience; US-based remote, so mainly feasible only with US work rights.</t>
+          <t>Genuine implementation/delivery role in health-tech that is described as suitable for early-career people, but it still asks for previous delivery experience and is London on-site, so KT would need to evidence project coordination (for example placements, audits, society or university projects) and UK right to work.</t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
@@ -6431,12 +6432,12 @@
       </c>
       <c r="X39" s="4" t="inlineStr">
         <is>
-          <t>https://thermofisher.wd5.myworkdayjobs.com/ThermoFisherCareers/job/Remote-North-Carolina-USA/Safety-Committee-Administrator_R-01370230</t>
+          <t>https://jobs.ashbyhq.com/tandem-health/cbe69db2-8030-4d6e-8b9d-298701bfaca1/application</t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t>Workday portal application; no other documents stated</t>
+          <t>CV in English (stated)</t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
@@ -6459,1072 +6460,14 @@
       <c r="AI39" s="3" t="inlineStr"/>
       <c r="AJ39" s="3" t="inlineStr"/>
     </row>
-    <row r="40">
-      <c r="A40" s="3" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>Pharmacovigilance / Drug Safety</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>Sr Assoc Pharmacovigilance Operations</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>Amgen</t>
-        </is>
-      </c>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="G40" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>India - Hyderabad</t>
-        </is>
-      </c>
-      <c r="I40" s="3" t="inlineStr">
-        <is>
-          <t>on-site</t>
-        </is>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="K40" s="3" t="inlineStr">
-        <is>
-          <t>Work mode on page: 'On Site'. No visa or residency wording; role is located in Hyderabad.</t>
-        </is>
-      </c>
-      <c r="L40" s="3" t="inlineStr">
-        <is>
-          <t>'Bachelor's degree and 2 years of directly related experience'</t>
-        </is>
-      </c>
-      <c r="M40" s="3" t="inlineStr">
-        <is>
-          <t>Bachelor's degree (with 2 years' experience) or associate's degree (6 years) or high school (8 years)</t>
-        </is>
-      </c>
-      <c r="N40" s="3" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="O40" s="3" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="P40" s="3" t="inlineStr">
-        <is>
-          <t>not stated</t>
-        </is>
-      </c>
-      <c r="Q40" s="3" t="inlineStr">
-        <is>
-          <t>- Bachelor's degree + 2 years related experience (or longer experience with lower education)
-- Case intake and processing knowledge
-- Understanding of expedited reporting to FDA/EMA
-- Vendor oversight support
-- Inspection readiness</t>
-        </is>
-      </c>
-      <c r="R40" s="3" t="inlineStr">
-        <is>
-          <t>- Support vendor oversight of case intake and processing
-- Case review and escalation of case-level issues
-- Reporting decisions for expedited safety reports to FDA/EMA
-- Support business-partner reconciliation
-- Support inspections and audits</t>
-        </is>
-      </c>
-      <c r="S40" s="3" t="inlineStr">
-        <is>
-          <t>case intake and processing; ICSRs; case review; expedited safety reports; FDA/EMA; vendor oversight; reconciliation; inspection readiness; PV System Master File</t>
-        </is>
-      </c>
-      <c r="T40" s="3" t="inlineStr">
-        <is>
-          <t>Regulatory reporting rules, ICSR evaluation and pharmacology.</t>
-        </is>
-      </c>
-      <c r="U40" s="3" t="inlineStr">
-        <is>
-          <t>2 years PV experience; on-site Hyderabad; no remote option.</t>
-        </is>
-      </c>
-      <c r="V40" s="3" t="inlineStr">
-        <is>
-          <t>Degree-level requirement plus 2 years of related experience; one clear gap. On-site in Hyderabad, so only workable if based in or relocating to India.</t>
-        </is>
-      </c>
-      <c r="W40" s="3" t="inlineStr">
-        <is>
-          <t>portal</t>
-        </is>
-      </c>
-      <c r="X40" s="4" t="inlineStr">
-        <is>
-          <t>https://amgen.wd1.myworkdayjobs.com/Careers/job/India---Hyderabad/Sr-Assoc-Pharmacovigilance-Operations_R-251859/apply</t>
-        </is>
-      </c>
-      <c r="Y40" s="3" t="inlineStr">
-        <is>
-          <t>Online application; no other documents stated</t>
-        </is>
-      </c>
-      <c r="Z40" s="3" t="inlineStr">
-        <is>
-          <t>none published: apply via the portal</t>
-        </is>
-      </c>
-      <c r="AA40" s="3" t="inlineStr"/>
-      <c r="AB40" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-18: OK</t>
-        </is>
-      </c>
-      <c r="AC40" s="3" t="inlineStr"/>
-      <c r="AD40" s="3" t="inlineStr"/>
-      <c r="AE40" s="3" t="inlineStr"/>
-      <c r="AF40" s="3" t="inlineStr"/>
-      <c r="AG40" s="3" t="inlineStr"/>
-      <c r="AH40" s="3" t="inlineStr"/>
-      <c r="AI40" s="3" t="inlineStr"/>
-      <c r="AJ40" s="3" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>Regulatory Affairs / Quality / Labelling / GxP</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>Local Contact Person for Pharmacovigilance and Regulatory Affairs (Contractor) - Germany</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>Ergomed Group (PrimeVigilance)</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>Berlin, Germany (remote)</t>
-        </is>
-      </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t>remote</t>
-        </is>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>unclear</t>
-        </is>
-      </c>
-      <c r="K41" s="3" t="inlineStr">
-        <is>
-          <t>SmartRecruiters location flag remote = true, hybrid = false, country de. Text says 'Employees can work remotely'. The job text refers to 'Australia', which looks like a copy-paste error from another country version. 'Proficiency in English and additional language knowledge is advantageous'. 'Bachelor's Degree in Life Sciences or Chemistry, Nursing or equivalent professional experience'.</t>
-        </is>
-      </c>
-      <c r="L41" s="3" t="inlineStr">
-        <is>
-          <t>At least 3 years of pharmacovigilance or safety-related experience in pharma, CRO or regulatory environment; prior RA experience preferred but not mandatory</t>
-        </is>
-      </c>
-      <c r="M41" s="3" t="inlineStr">
-        <is>
-          <t>Bachelor's degree in Life Sciences or Chemistry, Nursing, or equivalent professional experience</t>
-        </is>
-      </c>
-      <c r="N41" s="3" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="O41" s="3" t="inlineStr">
-        <is>
-          <t>English required; additional language advantageous (German not stated explicitly)</t>
-        </is>
-      </c>
-      <c r="P41" s="3" t="inlineStr">
-        <is>
-          <t>not stated</t>
-        </is>
-      </c>
-      <c r="Q41" s="3" t="inlineStr">
-        <is>
-          <t>- Life sciences, chemistry or nursing bachelor's degree
-- 3+ years pharmacovigilance or safety-related experience
-- Good understanding of ICH GVP and local PV requirements
-- Case handling, literature screening or local PV experience preferred
-- Regulatory affairs experience preferred but not mandatory
-- Microsoft Office skills</t>
-        </is>
-      </c>
-      <c r="R41" s="3" t="inlineStr">
-        <is>
-          <t>- Act as local person responsible for PV and RA and primary contact for local authorities
-- Collect and report locally suspected ADRs/ICSRs
-- Screen local literature and regulatory authority websites for safety information
-- Prepare documentation for regulatory submissions and review local product information and mock-ups
-- Handle local QA tasks such as falsified-product and quality alerts</t>
-        </is>
-      </c>
-      <c r="S41" s="3" t="inlineStr">
-        <is>
-          <t>ICH GVP; pharmacovigilance; ADRs; ICSRs; literature screening; regulatory intelligence; product information; local regulatory authorities; regulatory submissions; risk minimisation</t>
-        </is>
-      </c>
-      <c r="T41" s="3" t="inlineStr">
-        <is>
-          <t>Pharmacovigilance, ADR reporting, GVP, product information (SmPC/leaflet review), medicines law.</t>
-        </is>
-      </c>
-      <c r="U41" s="3" t="inlineStr">
-        <is>
-          <t>No 3 years of PV experience; local-representative roles usually need residence in the country, which the posting does not state; contractor status.</t>
-        </is>
-      </c>
-      <c r="V41" s="3" t="inlineStr">
-        <is>
-          <t>The 3-year PV experience requirement is the one clear gap; the degree fits and RA experience is not mandatory. The same template is posted for Paris, Brussels, Ljubljana, Athens and Budapest (all released 2026-10-13) and a Buenos Aires version (released 2026-10-16).</t>
-        </is>
-      </c>
-      <c r="W41" s="3" t="inlineStr">
-        <is>
-          <t>portal</t>
-        </is>
-      </c>
-      <c r="X41" s="4" t="inlineStr">
-        <is>
-          <t>https://jobs.smartrecruiters.com/Ergomed/744000155310319-local-contact-person-for-pharmacovigilance-and-regulatory-affairs-contractor-?oga=true</t>
-        </is>
-      </c>
-      <c r="Y41" s="3" t="inlineStr">
-        <is>
-          <t>Not stated (SmartRecruiters application)</t>
-        </is>
-      </c>
-      <c r="Z41" s="3" t="inlineStr">
-        <is>
-          <t>none published: apply via the portal</t>
-        </is>
-      </c>
-      <c r="AA41" s="3" t="inlineStr"/>
-      <c r="AB41" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-18: OK</t>
-        </is>
-      </c>
-      <c r="AC41" s="3" t="inlineStr"/>
-      <c r="AD41" s="3" t="inlineStr"/>
-      <c r="AE41" s="3" t="inlineStr"/>
-      <c r="AF41" s="3" t="inlineStr"/>
-      <c r="AG41" s="3" t="inlineStr"/>
-      <c r="AH41" s="3" t="inlineStr"/>
-      <c r="AI41" s="3" t="inlineStr"/>
-      <c r="AJ41" s="3" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>Medical information / medical affairs / medical writing / HEOR &amp; market access</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>Research Associate, MedTech Reimbursement &amp; Market Access (RHEMA)</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>IQVIA MedTech (MCRA)</t>
-        </is>
-      </c>
-      <c r="F42" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="G42" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>Washington, DC, United States</t>
-        </is>
-      </c>
-      <c r="I42" s="3" t="inlineStr">
-        <is>
-          <t>hybrid</t>
-        </is>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="K42" s="3" t="inlineStr">
-        <is>
-          <t>'This position is hybrid out of our Washington, DC office.' Degrees accepted: 'health economics, public health, health policy, epidemiology, economics, statistics, life sciences, or a related discipline'. No visa statement.</t>
-        </is>
-      </c>
-      <c r="L42" s="3" t="inlineStr">
-        <is>
-          <t>No years required; prior internship/academic/consulting/CRO/health-plan experience preferred</t>
-        </is>
-      </c>
-      <c r="M42" s="3" t="inlineStr">
-        <is>
-          <t>Bachelor's in health economics, public health, health policy, epidemiology, economics, statistics, life sciences or related; advanced degree preferred but not required</t>
-        </is>
-      </c>
-      <c r="N42" s="3" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="O42" s="3" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="P42" s="3" t="inlineStr">
-        <is>
-          <t>$58,700.00 - $146,800.00 (annualised base pay range printed on the posting)</t>
-        </is>
-      </c>
-      <c r="Q42" s="3" t="inlineStr">
-        <is>
-          <t>- Bachelor's in a related discipline (life sciences accepted)
-- Strong research, analytical, quantitative and writing skills
-- Familiarity with literature review, real-world evidence, health economics, PROs, publication research
-- Ability to organise multiple assignments and meet deadlines
-- Excellent written and oral communication
-- Word, PowerPoint and Excel proficiency</t>
-        </is>
-      </c>
-      <c r="R42" s="3" t="inlineStr">
-        <is>
-          <t>- Research Medicare/Medicaid/payer coverage, coding and payment policy
-- Run systematic and targeted literature searches and evidence-gap assessments
-- Support HEOR, burden-of-illness and budget-impact analyses under a project lead
-- Support publication planning, evidence-generation plans and value tools
-- Prepare Word/PowerPoint/Excel deliverables and present findings</t>
-        </is>
-      </c>
-      <c r="S42" s="3" t="inlineStr">
-        <is>
-          <t>literature searches; evidence landscape reviews; evidence-gap assessments; real-world evidence; health economics and outcomes research; burden-of-illness analyses; publication planning; payer; Word, PowerPoint and Excel; reimbursement</t>
-        </is>
-      </c>
-      <c r="T42" s="3" t="inlineStr">
-        <is>
-          <t>Literature searching, evidence appraisal, pharmacoeconomics module content, healthcare-system knowledge.</t>
-        </is>
-      </c>
-      <c r="U42" s="3" t="inlineStr">
-        <is>
-          <t>US location/work authorisation; US payer-policy knowledge (Medicare/Medicaid); the posting shows no sponsorship statement.</t>
-        </is>
-      </c>
-      <c r="V42" s="3" t="inlineStr">
-        <is>
-          <t>Qualifications are within reach (life-science degree, no years required), but it is a hybrid Washington DC role for a US healthcare-policy audience, so KT would need US work authorisation and relocation.</t>
-        </is>
-      </c>
-      <c r="W42" s="3" t="inlineStr">
-        <is>
-          <t>portal</t>
-        </is>
-      </c>
-      <c r="X42" s="4" t="inlineStr">
-        <is>
-          <t>https://iqvia.wd1.myworkdayjobs.com/IQVIA/job/Washington-DC-United-States-of-America/Research-Associate--Reimbursement--Health-Economics---Market-Access_R1572565/apply</t>
-        </is>
-      </c>
-      <c r="Y42" s="3" t="inlineStr">
-        <is>
-          <t>Not stated (Workday portal; CV)</t>
-        </is>
-      </c>
-      <c r="Z42" s="3" t="inlineStr">
-        <is>
-          <t>none published: apply via the portal</t>
-        </is>
-      </c>
-      <c r="AA42" s="3" t="inlineStr"/>
-      <c r="AB42" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-18: OK</t>
-        </is>
-      </c>
-      <c r="AC42" s="3" t="inlineStr"/>
-      <c r="AD42" s="3" t="inlineStr"/>
-      <c r="AE42" s="3" t="inlineStr"/>
-      <c r="AF42" s="3" t="inlineStr"/>
-      <c r="AG42" s="3" t="inlineStr"/>
-      <c r="AH42" s="3" t="inlineStr"/>
-      <c r="AI42" s="3" t="inlineStr"/>
-      <c r="AJ42" s="3" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>Medical information / medical affairs / medical writing / HEOR &amp; market access</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>Medical Information Associate</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>Novartis</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="G43" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t>Seoul (South Korea)</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t>unclear</t>
-        </is>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>unclear</t>
-        </is>
-      </c>
-      <c r="K43" s="3" t="inlineStr">
-        <is>
-          <t>Location: Seoul. 'Bachelor's degree in Life Sciences or a relevant healthcare discipline, such as pharmacy, nursing or medicine.' 'Excellent customer service, communication, English reading and writing skills.' Work mode not stated; the role works 'in line with local regulations', so a Korean-market role. Korean is not mentioned in the text.</t>
-        </is>
-      </c>
-      <c r="L43" s="3" t="inlineStr">
-        <is>
-          <t>At least one year of experience in a healthcare setting</t>
-        </is>
-      </c>
-      <c r="M43" s="3" t="inlineStr">
-        <is>
-          <t>Bachelor's in life sciences or healthcare discipline (pharmacy accepted)</t>
-        </is>
-      </c>
-      <c r="N43" s="3" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="O43" s="3" t="inlineStr">
-        <is>
-          <t>English reading/writing; Korean not mentioned but the market is Korea</t>
-        </is>
-      </c>
-      <c r="P43" s="3" t="inlineStr">
-        <is>
-          <t>not stated</t>
-        </is>
-      </c>
-      <c r="Q43" s="3" t="inlineStr">
-        <is>
-          <t>- Bachelor's in life sciences/pharmacy/nursing/medicine
-- At least 1 year of experience in a healthcare setting
-- Strong scientific and medical knowledge
-- Proficiency in databases/systems used for medical information
-- Excellent customer service and communication
-- Detail-oriented, compliance-minded</t>
-        </is>
-      </c>
-      <c r="R43" s="3" t="inlineStr">
-        <is>
-          <t>- Answer unsolicited medical enquiries accurately and on time
-- Develop and maintain medical information responses from approved data and current evidence
-- Run literature searches and critically evaluate data
-- Document enquiries and rationale in medical information systems
-- Review promotional/non-promotional content for scientific accuracy
-- Share aggregated insights on recurring questions and evidence gaps</t>
-        </is>
-      </c>
-      <c r="S43" s="3" t="inlineStr">
-        <is>
-          <t>unsolicited medical enquiries; non-promotional; literature searches; critically evaluate scientific data; medical information systems; scientific accuracy; approved scientific data; healthcare setting; customer service; compliance</t>
-        </is>
-      </c>
-      <c r="T43" s="3" t="inlineStr">
-        <is>
-          <t>Drug information, literature evaluation, evidence appraisal, regulatory awareness.</t>
-        </is>
-      </c>
-      <c r="U43" s="3" t="inlineStr">
-        <is>
-          <t>1 year healthcare-setting experience; Seoul location; Korean language probably needed in practice (not stated).</t>
-        </is>
-      </c>
-      <c r="V43" s="3" t="inlineStr">
-        <is>
-          <t>Pharmacy is named as an accepted degree and the duties are classic medical information; the gap is 1 year in a healthcare setting (MPharm placements may count) and the Seoul location with probable Korean-language need.</t>
-        </is>
-      </c>
-      <c r="W43" s="3" t="inlineStr">
-        <is>
-          <t>portal</t>
-        </is>
-      </c>
-      <c r="X43" s="4" t="inlineStr">
-        <is>
-          <t>https://novartis.wd3.myworkdayjobs.com/Novartis_Careers/job/Seoul/Medical-Information-Associate_REQ-10087203/apply</t>
-        </is>
-      </c>
-      <c r="Y43" s="3" t="inlineStr">
-        <is>
-          <t>Not stated (Workday portal; CV)</t>
-        </is>
-      </c>
-      <c r="Z43" s="3" t="inlineStr">
-        <is>
-          <t>none published: apply via the portal</t>
-        </is>
-      </c>
-      <c r="AA43" s="3" t="inlineStr"/>
-      <c r="AB43" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-18: OK</t>
-        </is>
-      </c>
-      <c r="AC43" s="3" t="inlineStr"/>
-      <c r="AD43" s="3" t="inlineStr"/>
-      <c r="AE43" s="3" t="inlineStr"/>
-      <c r="AF43" s="3" t="inlineStr"/>
-      <c r="AG43" s="3" t="inlineStr"/>
-      <c r="AH43" s="3" t="inlineStr"/>
-      <c r="AI43" s="3" t="inlineStr"/>
-      <c r="AJ43" s="3" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>Regulatory Affairs / Quality / Labelling / GxP</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>Quality and Compliance Assistant</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t>Labcorp</t>
-        </is>
-      </c>
-      <c r="F44" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="G44" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>Bengaluru, India</t>
-        </is>
-      </c>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t>remote</t>
-        </is>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>unclear</t>
-        </is>
-      </c>
-      <c r="K44" s="3" t="inlineStr">
-        <is>
-          <t>'Labcorp is seeking a remote Quality and Compliance Assistant'; 'Remote based'; schedule 'Monday - Friday, 2PM - 11PM'. No work-authorisation wording; location Bengaluru, India.</t>
-        </is>
-      </c>
-      <c r="L44" s="3" t="inlineStr">
-        <is>
-          <t>1 year of experience in the job discipline</t>
-        </is>
-      </c>
-      <c r="M44" s="3" t="inlineStr">
-        <is>
-          <t>Master's degree in life sciences (preferred: associate degree level of laboratory or animal technician, biological sciences, pharmacy or medical nurse, or equivalent)</t>
-        </is>
-      </c>
-      <c r="N44" s="3" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="O44" s="3" t="inlineStr">
-        <is>
-          <t>Good English speaking, writing and reading</t>
-        </is>
-      </c>
-      <c r="P44" s="3" t="inlineStr">
-        <is>
-          <t>not stated</t>
-        </is>
-      </c>
-      <c r="Q44" s="3" t="inlineStr">
-        <is>
-          <t>- Master's degree in life sciences
-- 1 year of experience in the job discipline
-- Good English communication
-- Time management
-- MS Office user knowledge
-- Attention to detail</t>
-        </is>
-      </c>
-      <c r="R44" s="3" t="inlineStr">
-        <is>
-          <t>- Administrative tasks for the Quality and Compliance group
-- Support metric collation
-- Learn Veeva Quality Systems
-- Assist in Customer Hallmark Health Check discussions
-- Work under regular supervision</t>
-        </is>
-      </c>
-      <c r="S44" s="3" t="inlineStr">
-        <is>
-          <t>Quality and Compliance; Veeva Quality Systems; metrics; attention to detail; time management; MS Office; Master's degree in life sciences</t>
-        </is>
-      </c>
-      <c r="T44" s="3" t="inlineStr">
-        <is>
-          <t>GxP and quality system awareness, document control concepts.</t>
-        </is>
-      </c>
-      <c r="U44" s="3" t="inlineStr">
-        <is>
-          <t>No year of industry quality experience; role is tied to India time zone and posting does not say whether non-residents can apply.</t>
-        </is>
-      </c>
-      <c r="V44" s="3" t="inlineStr">
-        <is>
-          <t>KT meets the master's-level education line, but one year in the discipline is asked and the schedule is a late-day shift (2PM-11PM) in India. Administrative entry role in a GxP quality group.</t>
-        </is>
-      </c>
-      <c r="W44" s="3" t="inlineStr">
-        <is>
-          <t>portal</t>
-        </is>
-      </c>
-      <c r="X44" s="4" t="inlineStr">
-        <is>
-          <t>https://labcorp.wd1.myworkdayjobs.com/External/job/Bengaluru-India/Quality-and-Compliance-Assistant_2633009</t>
-        </is>
-      </c>
-      <c r="Y44" s="3" t="inlineStr">
-        <is>
-          <t>Not stated (Workday portal; CV expected)</t>
-        </is>
-      </c>
-      <c r="Z44" s="3" t="inlineStr">
-        <is>
-          <t>none published: apply via the portal</t>
-        </is>
-      </c>
-      <c r="AA44" s="3" t="inlineStr"/>
-      <c r="AB44" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-18: OK</t>
-        </is>
-      </c>
-      <c r="AC44" s="3" t="inlineStr"/>
-      <c r="AD44" s="3" t="inlineStr"/>
-      <c r="AE44" s="3" t="inlineStr"/>
-      <c r="AF44" s="3" t="inlineStr"/>
-      <c r="AG44" s="3" t="inlineStr"/>
-      <c r="AH44" s="3" t="inlineStr"/>
-      <c r="AI44" s="3" t="inlineStr"/>
-      <c r="AJ44" s="3" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>Pharmacovigilance / Drug Safety</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>Senior Pharmacovigilance Associate (ICSR management; Kraków, remote; same title also posted for Cluj-Napoca, Romania)</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="inlineStr">
-        <is>
-          <t>PrimeVigilance (Ergomed Group)</t>
-        </is>
-      </c>
-      <c r="F45" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="G45" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t>Kraków, Poland (remote flag). Also: Cluj-Napoca, Romania, remote flag, https://jobs.smartrecruiters.com/Ergomed/744000154954939-senior-pharmacovigilance-associate (posted 2026-10-12); Bucharest is hybrid</t>
-        </is>
-      </c>
-      <c r="I45" s="3" t="inlineStr">
-        <is>
-          <t>remote</t>
-        </is>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>unclear</t>
-        </is>
-      </c>
-      <c r="K45" s="3" t="inlineStr">
-        <is>
-          <t>Location tied to Poland/Romania; 'English - advanced (spoken, written)'; role includes acting as LCPPV and PRLS for the specified country and language 'as agreed with the line manager'. No visa wording.</t>
-        </is>
-      </c>
-      <c r="L45" s="3" t="inlineStr">
-        <is>
-          <t>'Minimum 1 year of work experience in pharmacovigilance'</t>
-        </is>
-      </c>
-      <c r="M45" s="3" t="inlineStr">
-        <is>
-          <t>'Life science graduate, pharmacy, nursing, other healthcare related qualification or experience in pharmacovigilance'</t>
-        </is>
-      </c>
-      <c r="N45" s="3" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="O45" s="3" t="inlineStr">
-        <is>
-          <t>English advanced (spoken and written); local-language duties may apply</t>
-        </is>
-      </c>
-      <c r="P45" s="3" t="inlineStr">
-        <is>
-          <t>not stated</t>
-        </is>
-      </c>
-      <c r="Q45" s="3" t="inlineStr">
-        <is>
-          <t>- Life science / pharmacy / nursing graduate or PV experience
-- Minimum 1 year of PV work experience
-- Advanced English
-- Organisation skills and attention to detail
-- Time and issue management
-- Advanced MS Office literacy</t>
-        </is>
-      </c>
-      <c r="R45" s="3" t="inlineStr">
-        <is>
-          <t>- Process ICSRs from all sources to regulations and client timelines; ICSR follow-up
-- SAE/SUSAR management incl. reconciliation, protocol and Safety Management Plan review
-- Product quality complaint handling and medical information interaction
-- MedDRA and WHO coding
-- Database outputs and monthly client reports; may act as LCPPV/PRLS for a country</t>
-        </is>
-      </c>
-      <c r="S45" s="3" t="inlineStr">
-        <is>
-          <t>Individual Case Safety Reports (ICSRs); ICSR follow up; SAE/SUSAR Management; reconciliation; Product Quality Complaint handling; MedDRA and WHO coding; Safety Management Plan; personal data protection; Local Contact Person for Pharmacovigilance (LCPPV)</t>
-        </is>
-      </c>
-      <c r="T45" s="3" t="inlineStr">
-        <is>
-          <t>Pharmacy degree is named; MedDRA/WHO drug coding, ADR assessment, quality complaints and regulatory reporting map onto MPharm content.</t>
-        </is>
-      </c>
-      <c r="U45" s="3" t="inlineStr">
-        <is>
-          <t>Minimum 1 year PV experience; Poland/Romania residency likely needed; possible local language duties.</t>
-        </is>
-      </c>
-      <c r="V45" s="3" t="inlineStr">
-        <is>
-          <t>Pharmacy graduate is an accepted background and the role is tagged Entry Level on the ATS, but it asks for at least 1 year of PV work experience despite the 'Senior' title. Location is tied to Poland/Romania.</t>
-        </is>
-      </c>
-      <c r="W45" s="3" t="inlineStr">
-        <is>
-          <t>portal</t>
-        </is>
-      </c>
-      <c r="X45" s="4" t="inlineStr">
-        <is>
-          <t>https://jobs.smartrecruiters.com/Ergomed/744000154955029-senior-pharmacovigilance-associate?oga=true</t>
-        </is>
-      </c>
-      <c r="Y45" s="3" t="inlineStr">
-        <is>
-          <t>Online application on SmartRecruiters; no other documents stated</t>
-        </is>
-      </c>
-      <c r="Z45" s="3" t="inlineStr">
-        <is>
-          <t>none published: apply via the portal</t>
-        </is>
-      </c>
-      <c r="AA45" s="3" t="inlineStr"/>
-      <c r="AB45" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-18: OK</t>
-        </is>
-      </c>
-      <c r="AC45" s="3" t="inlineStr"/>
-      <c r="AD45" s="3" t="inlineStr"/>
-      <c r="AE45" s="3" t="inlineStr"/>
-      <c r="AF45" s="3" t="inlineStr"/>
-      <c r="AG45" s="3" t="inlineStr"/>
-      <c r="AH45" s="3" t="inlineStr"/>
-      <c r="AI45" s="3" t="inlineStr"/>
-      <c r="AJ45" s="3" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>Healthcare operations / implementation / customer success / clinical product / pharmacy operations</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>Project Delivery Specialist</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="inlineStr">
-        <is>
-          <t>Tandem Health</t>
-        </is>
-      </c>
-      <c r="F46" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="G46" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t>London (on site; frequent customer-site travel across the UK, occasional trips to Stockholm)</t>
-        </is>
-      </c>
-      <c r="I46" s="3" t="inlineStr">
-        <is>
-          <t>on-site</t>
-        </is>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>unclear</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="inlineStr">
-        <is>
-          <t>No visa or residency wording. 'Ashby workplaceType = OnSite'; London office working day is part of the interview process; 'frequent trips to customer sites across the UK'</t>
-        </is>
-      </c>
-      <c r="L46" s="3" t="inlineStr">
-        <is>
-          <t>'You've delivered rollouts before' in delivery, project, implementation or customer onboarding roles; 'ideal for somebody early in their career'</t>
-        </is>
-      </c>
-      <c r="M46" s="3" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="N46" s="3" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="O46" s="3" t="inlineStr">
-        <is>
-          <t>English (CV in English)</t>
-        </is>
-      </c>
-      <c r="P46" s="3" t="inlineStr">
-        <is>
-          <t>not stated</t>
-        </is>
-      </c>
-      <c r="Q46" s="3" t="inlineStr">
-        <is>
-          <t>- Has delivered rollouts before in delivery/project/implementation/customer-onboarding roles
-- Comfortable with implementation plans, governance, RAID logs, dependencies and reporting
-- Experience of NHS and/or private healthcare environments is 'ideally' wanted
-- Confident with senior and frontline stakeholders
-- Willing to travel frequently to UK customer sites
-- Nice to have: digital health/SaaS implementations in regulated settings
-- Nice to have: NHS governance/IG (DPIA, DCB standards, DTAC)</t>
-        </is>
-      </c>
-      <c r="R46" s="3" t="inlineStr">
-        <is>
-          <t>- Run several implementations in parallel with 60-90 day plans from kickoff to go-live
-- Keep customer clinical, ops and IT leads aligned with Medical Ops, Product, Engineering and Commercial
-- Spot risks early and unblock issues
-- Coordinate training, comms and support readiness and track adoption after go-live
-- Build repeatable delivery playbooks and templates</t>
-        </is>
-      </c>
-      <c r="S46" s="3" t="inlineStr">
-        <is>
-          <t>implementation plans; go-live; rollout; stakeholders; RAID; dependencies; adoption; playbooks; NHS; digital health; regulated; customer onboarding</t>
-        </is>
-      </c>
-      <c r="T46" s="3" t="inlineStr">
-        <is>
-          <t>Understanding of clinical settings and NHS medicines governance; pharmacy placements give exposure to how clinicians and IT interact.</t>
-        </is>
-      </c>
-      <c r="U46" s="3" t="inlineStr">
-        <is>
-          <t>No stated implementation/project delivery experience. On-site in London. Right to work not stated but implied UK.</t>
-        </is>
-      </c>
-      <c r="V46" s="3" t="inlineStr">
-        <is>
-          <t>Genuine implementation/delivery role in health-tech that is described as suitable for early-career people, but it still asks for previous delivery experience and is London on-site, so KT would need to evidence project coordination (for example placements, audits, society or university projects) and UK right to work.</t>
-        </is>
-      </c>
-      <c r="W46" s="3" t="inlineStr">
-        <is>
-          <t>portal</t>
-        </is>
-      </c>
-      <c r="X46" s="4" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/tandem-health/cbe69db2-8030-4d6e-8b9d-298701bfaca1/application</t>
-        </is>
-      </c>
-      <c r="Y46" s="3" t="inlineStr">
-        <is>
-          <t>CV in English (stated)</t>
-        </is>
-      </c>
-      <c r="Z46" s="3" t="inlineStr">
-        <is>
-          <t>none published: apply via the portal</t>
-        </is>
-      </c>
-      <c r="AA46" s="3" t="inlineStr"/>
-      <c r="AB46" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-18: OK</t>
-        </is>
-      </c>
-      <c r="AC46" s="3" t="inlineStr"/>
-      <c r="AD46" s="3" t="inlineStr"/>
-      <c r="AE46" s="3" t="inlineStr"/>
-      <c r="AF46" s="3" t="inlineStr"/>
-      <c r="AG46" s="3" t="inlineStr"/>
-      <c r="AH46" s="3" t="inlineStr"/>
-      <c r="AI46" s="3" t="inlineStr"/>
-      <c r="AJ46" s="3" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ46"/>
-  <conditionalFormatting sqref="G2:G46">
+  <autoFilter ref="A1:AJ39"/>
+  <conditionalFormatting sqref="G2:G39">
     <cfRule type="cellIs" priority="1" operator="greaterThanOrEqual" dxfId="0">
       <formula>6</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B46">
+  <conditionalFormatting sqref="B2:B39">
     <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
       <formula>"A"</formula>
     </cfRule>
@@ -7533,7 +6476,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="AC2:AG46" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AC2:AG39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7576,13 +6519,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X37" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X38" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X39" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X40" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X41" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X42" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X43" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X44" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X45" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X46" r:id="rId45"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7594,7 +6530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7688,12 +6624,12 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Regulatory Submissions Associate Manager II (EU CTR / CTIS)</t>
+          <t>Medical Writer III (Pharmacovigilance)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Fortrea</t>
+          <t>Ergomed / PrimeVigilance</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -7703,17 +6639,17 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Leeds, United Kingdom (additional location: Remote United Kingdom)</t>
+          <t>Zagreb, Croatia (remote)</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>https://fortrea.wd1.myworkdayjobs.com/Fortrea/job/Leeds/Regulatory-Submissions-Ass-Manager-II_266235</t>
+          <t>https://jobs.smartrecruiters.com/Ergomed/744000155975969-medical-writer-iii-pharmacovigilance-</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Needs 4 years plus hands-on CTIS experience; it is a mid-level manager grade.</t>
+          <t>Pharmacy degree is explicitly welcome and the role is remote, but it needs 2 years in medical writing/PV and mentoring ability, which KT does not have yet. Audit: Level III role, 2-year medical-writing minimum, and it requires mentoring junior writers.</t>
         </is>
       </c>
     </row>
@@ -7725,12 +6661,12 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Senior Product Manager (Healthcare Data Products/API)</t>
+          <t>Regulatory Submissions Associate Manager II (EU CTR / CTIS)</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Inovalon</t>
+          <t>Fortrea</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -7740,17 +6676,17 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>REMOTE - US</t>
+          <t>Leeds, United Kingdom (additional location: Remote United Kingdom)</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/inovalon/e0e57ecf-0fc1-42e4-9c21-3ebe30207a3c</t>
+          <t>https://fortrea.wd1.myworkdayjobs.com/Fortrea/job/Leeds/Regulatory-Submissions-Ass-Manager-II_266235</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Senior, 8+ years required.</t>
+          <t>Needs 4 years plus hands-on CTIS experience; it is a mid-level manager grade.</t>
         </is>
       </c>
     </row>
@@ -7762,12 +6698,12 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Associate Market Access Manager</t>
+          <t>Clinical Trial Safety Scientist (FSP - Permanent Home Based)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson (Innovative Medicine)</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -7777,17 +6713,17 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Petaling Jaya, Selangor, Malaysia</t>
+          <t>Madrid, Spain; Barcelona, Spain (home-based)</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>https://jj.wd5.myworkdayjobs.com/JJ/job/Petaling-Jaya-Selangor-Malaysia/Associate-Market-Access-Manager_R-105370</t>
+          <t>https://jobs.iqvia.com/en/jobs/R1521994-1</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Pharmacy degree is named, but 3 years of market access experience plus Malaysia-specific knowledge are required.</t>
+          <t>Needs 2+ years of PV experience (clear gap) but an MPharm meets the degree line and the role is home-based within a CRO FSP model. Same standard as the audit: scientist role with a stated minimum of 2+ years in pharmacovigilance.</t>
         </is>
       </c>
     </row>
@@ -7799,12 +6735,12 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Clinical Programs Specialist</t>
+          <t>Senior Product Manager (Healthcare Data Products/API)</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Judi Health</t>
+          <t>Inovalon</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -7814,17 +6750,17 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Remote, US (listed offices Charlotte, Denver, New York)</t>
+          <t>REMOTE - US</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/judihealth/jobs/5454128008</t>
+          <t>https://jobs.ashbyhq.com/inovalon/e0e57ecf-0fc1-42e4-9c21-3ebe30207a3c</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>Requires an active US healthcare licence and US-based remote work; KT has neither. Duties are a good template for the type of PBM clinical-programme operations role to look for elsewhere.</t>
+          <t>Senior, 8+ years required.</t>
         </is>
       </c>
     </row>
@@ -7836,12 +6772,12 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Clinical Review Pharmacist (6-month, full-time contract)</t>
+          <t>Associate Market Access Manager</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>SmithRx</t>
+          <t>Johnson &amp; Johnson (Innovative Medicine)</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -7851,17 +6787,17 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>US - Remote</t>
+          <t>Petaling Jaya, Selangor, Malaysia</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/smithrx/jobs/8896130002</t>
+          <t>https://jj.wd5.myworkdayjobs.com/JJ/job/Petaling-Jaya-Selangor-Malaysia/Associate-Market-Access-Manager_R-105370</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Needs an active US pharmacist licence and 2 years of practice; KT is unlicensed and the role is US-resident only.</t>
+          <t>Pharmacy degree is named, but 3 years of market access experience plus Malaysia-specific knowledge are required.</t>
         </is>
       </c>
     </row>
@@ -7873,12 +6809,12 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Medical Operations - Spain</t>
+          <t>Clinical Programs Specialist</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Tandem Health</t>
+          <t>Judi Health</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -7888,17 +6824,17 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Madrid, Spain (Ashby says remote, but the text says regular in-person attendance at the Madrid office)</t>
+          <t>Remote, US (listed offices Charlotte, Denver, New York)</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/tandem-health/9eb14d41-3610-4899-ae20-a893b298a1d9</t>
+          <t>https://job-boards.greenhouse.io/judihealth/jobs/5454128008</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>Wants a medical doctor, Spanish fluency and Madrid office attendance.</t>
+          <t>Requires an active US healthcare licence and US-based remote work; KT has neither. Duties are a good template for the type of PBM clinical-programme operations role to look for elsewhere.</t>
         </is>
       </c>
     </row>
@@ -7910,12 +6846,12 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Medical Information Specialist - Nurse</t>
+          <t>Clinical Review Pharmacist (6-month, full-time contract)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific (PPD clinical research)</t>
+          <t>SmithRx</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -7925,17 +6861,17 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Morrisville, North Carolina, USA</t>
+          <t>US - Remote</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>https://thermofisher.wd5.myworkdayjobs.com/ThermoFisherCareers/job/Morrisville-North-Carolina-USA/Medical-Information-Specialist---Nurse_R-01371120</t>
+          <t>https://job-boards.greenhouse.io/smithrx/jobs/8896130002</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Requires an active US RN licence, which KT cannot hold as an unlicensed pharmacy graduate. Listed only so KT can see that two identical 'Nurse' medical information postings exist at PPD (R-01371114 and R-01371120).</t>
+          <t>Needs an active US pharmacist licence and 2 years of practice; KT is unlicensed and the role is US-resident only.</t>
         </is>
       </c>
     </row>
@@ -7947,32 +6883,32 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Manager, Medical Operations, EU West</t>
+          <t>Medical Operations - Spain</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>BridgeBio</t>
+          <t>Tandem Health</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Remote - France (France-based role, Paris area designated office)</t>
+          <t>Madrid, Spain (Ashby says remote, but the text says regular in-person attendance at the Madrid office)</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/bridgebio/jobs/5265684007</t>
+          <t>https://jobs.ashbyhq.com/tandem-health/9eb14d41-3610-4899-ae20-a893b298a1d9</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>France-based, French fluency and 2-5 years of Medical Affairs operations required; a strong role type for the future.</t>
+          <t>Wants a medical doctor, Spanish fluency and Madrid office attendance.</t>
         </is>
       </c>
     </row>
@@ -7984,32 +6920,32 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Pharmacovigilance Associate</t>
+          <t>Medical Writer - Medical Information</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Cencora (Canada)</t>
+          <t>Thermo Fisher Scientific (PPD clinical research)</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Remote, Ontario, Canada</t>
+          <t>Remote, Massachusetts, USA</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>https://careers.cencora.com/us/en/job/R2617964/Pharmacovigilance-Associate</t>
+          <t>https://thermofisher.wd5.myworkdayjobs.com/ThermoFisherCareers/job/Remote-Massachusetts-USA/Medical-Writer---Medical-Information_R-01364891-1</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>Requires 3+ years' experience and includes mentoring junior staff; too much for a new graduate.</t>
+          <t>One clear gap: the posting asks for experience 'comparable to 2+ years' and it is a US-based remote role with a Massachusetts pay scale, with no statement that non-US residents can apply. The writing content (medical information documents, publications) fits an MPharm well. Same standard as the audit: needs about 2+ years of writing/pharma-CRO experience.</t>
         </is>
       </c>
     </row>
@@ -8021,32 +6957,32 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Principal, Clinical Product</t>
+          <t>Medical Information Specialist - Nurse</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Headway</t>
+          <t>Thermo Fisher Scientific (PPD clinical research)</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Remote (company hires remotely across the US)</t>
+          <t>Morrisville, North Carolina, USA</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/headway/06b24a61-e976-4e78-8a8a-03e10b3be5df</t>
+          <t>https://thermofisher.wd5.myworkdayjobs.com/ThermoFisherCareers/job/Morrisville-North-Carolina-USA/Medical-Information-Specialist---Nurse_R-01371120</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>Doctoral clinical licence and 6+ years required; principal level.</t>
+          <t>Requires an active US RN licence, which KT cannot hold as an unlicensed pharmacy graduate. Listed only so KT can see that two identical 'Nurse' medical information postings exist at PPD (R-01371114 and R-01371120).</t>
         </is>
       </c>
     </row>
@@ -8058,12 +6994,12 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Clinical Trials Regulatory Officer 2 (Regulatory Maintenance Associate)</t>
+          <t>Manager, Medical Operations, EU West</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>IQVIA</t>
+          <t>BridgeBio</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -8073,17 +7009,17 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Zagreb, Croatia; additional locations: Belgrade, Lisbon, Kyiv, Kiel, Sofia, Madrid, Bucharest</t>
+          <t>Remote - France (France-based role, Paris area designated office)</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>https://iqvia.wd1.myworkdayjobs.com/IQVIA/job/Zagreb-Croatia/Clinical-Trials-Regulatory-Officer---Regulatory-Maintenance_R1568332-1</t>
+          <t>https://job-boards.greenhouse.io/bridgebio/jobs/5265684007</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Pharmacy is a named degree, but 3 years of hands-on CTIS submission experience is required; not realistic yet. A useful stepping-stone target after ICON/IQVIA start-up roles.</t>
+          <t>France-based, French fluency and 2-5 years of Medical Affairs operations required; a strong role type for the future.</t>
         </is>
       </c>
     </row>
@@ -8095,12 +7031,12 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Assoc. Spclst, Drug Safety (local PV)</t>
+          <t>Pharmacovigilance Associate</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>MSD (Merck Sharp &amp; Dohme)</t>
+          <t>Cencora (Canada)</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -8110,17 +7046,17 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Jakarta, Indonesia</t>
+          <t>Remote, Ontario, Canada</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>https://msd.wd5.myworkdayjobs.com/SearchJobs/job/IDN---Jakarta---Jakarta-Menara-Astra/Assoc-Spclst--Drug-Safety_R422379</t>
+          <t>https://careers.cencora.com/us/en/job/R2617964/Pharmacovigilance-Associate</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>Entry-level in content (experience only preferred) but hybrid in Jakarta and requires local-language proficiency, so not realistic unless based in Indonesia.</t>
+          <t>Requires 3+ years' experience and includes mentoring junior staff; too much for a new graduate.</t>
         </is>
       </c>
     </row>
@@ -8132,12 +7068,12 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Clinical Research Associate I / Clinical Research Associate II (France)</t>
+          <t>Principal, Clinical Product</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Precision for Medicine (Precision Medicine Group)</t>
+          <t>Headway</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -8147,17 +7083,17 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Remote, France ('looking for candidates based in Paris or Paris area')</t>
+          <t>Remote (company hires remotely across the US)</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/precisionmedicinegroup/jobs/6129671004</t>
+          <t>https://jobs.ashbyhq.com/headway/06b24a61-e976-4e78-8a8a-03e10b3be5df</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Requires prior CRA experience, French fluency, oncology experience and a Paris base.</t>
+          <t>Doctoral clinical licence and 6+ years required; principal level.</t>
         </is>
       </c>
     </row>
@@ -8169,12 +7105,12 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Country Regulatory Specialist, Clinical Research - 100% Remote in Brazil, English advanced</t>
+          <t>Clinical Trials Regulatory Officer 2 (Regulatory Maintenance Associate)</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Syneos Health</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -8184,17 +7120,17 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Remote, Brazil</t>
+          <t>Zagreb, Croatia; additional locations: Belgrade, Lisbon, Kyiv, Kiel, Sofia, Madrid, Bucharest</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>https://www.syneoshealth.com/clinical-corporate-careers/jobs/18363943-country-regulatory-specialist-clinical-research-100-percent-remote-in-brazil-english-advanced</t>
+          <t>https://iqvia.wd1.myworkdayjobs.com/IQVIA/job/Zagreb-Croatia/Clinical-Trials-Regulatory-Officer---Regulatory-Maintenance_R1568332-1</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>Needs 3-4 years of clinical research experience and a Brazil base.</t>
+          <t>Pharmacy is a named degree, but 3 years of hands-on CTIS submission experience is required; not realistic yet. A useful stepping-stone target after ICON/IQVIA start-up roles.</t>
         </is>
       </c>
     </row>
@@ -8206,12 +7142,12 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Assistant CRA - FSP (Brazil, remote)</t>
+          <t>Assoc. Spclst, Drug Safety (local PV)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific (PPD clinical research business)</t>
+          <t>MSD (Merck Sharp &amp; Dohme)</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -8221,17 +7157,17 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Brazil - Sao Paulo - Remote</t>
+          <t>Jakarta, Indonesia</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>https://thermofisher.wd5.myworkdayjobs.com/ThermoFisherCareers/job/Remote-Brazil/Assistant-CRA---FSP_R-01371844</t>
+          <t>https://msd.wd5.myworkdayjobs.com/SearchJobs/job/IDN---Jakarta---Jakarta-Menara-Astra/Assoc-Spclst--Drug-Safety_R422379</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>Headline says 0-2 years but the posting makes prior oncology clinical-study experience mandatory and is Brazil-based.</t>
+          <t>Entry-level in content (experience only preferred) but hybrid in Jakarta and requires local-language proficiency, so not realistic unless based in Indonesia.</t>
         </is>
       </c>
     </row>
@@ -8243,32 +7179,32 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Medical Information Specialist with Latvian, English and Additional Language</t>
+          <t>Site Contract Specialist I</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>IQVIA</t>
+          <t>PSI CRO</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Riga, Latvia (also Lisbon, Zagreb, Athens, Barcelona, Prague, Sofia, Madrid, Bucharest)</t>
+          <t>Mexico City, Mexico - 'Home-based position in Mexico'</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>https://iqvia.wd1.myworkdayjobs.com/IQVIA/job/Riga-Latvia/Medical-Information-Specialist-with-Latvian--English-and-Additional-Language_R1573442</t>
+          <t>https://jobs.smartrecruiters.com/PSICRO/744000155843309-site-contract-specialist-i-</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>Perfect on duties and degree (no experience asked), but Latvian at C2 level is a hard requirement KT almost certainly lacks. IQVIA posts the same job for other languages (Bulgarian dated 2026-10-09, German/Estonian variants), all language-gated.</t>
+          <t>Entry Level label, but the text requires prior study start-up experience, Spanish fluency and a Mexico base. Audit: study start-up experience is required and Spanish fluency is required; two clear gaps.</t>
         </is>
       </c>
     </row>
@@ -8280,32 +7216,32 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Clinical Pharmacist (Independent Prescriber)</t>
+          <t>Clinical Research Associate I / Clinical Research Associate II (France)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Montu UK (Alternaleaf)</t>
+          <t>Precision for Medicine (Precision Medicine Group)</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Hybrid London, UK</t>
+          <t>Remote, France ('looking for candidates based in Paris or Paris area')</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/montu-uk/4435f8d7-0eeb-46f8-85fc-f6784ed0ba62</t>
+          <t>https://job-boards.greenhouse.io/precisionmedicinegroup/jobs/6129671004</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>Requires GPhC registration and IP qualification.</t>
+          <t>Requires prior CRA experience, French fluency, oncology experience and a Paris base.</t>
         </is>
       </c>
     </row>
@@ -8317,32 +7253,32 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Patient Safety Specialist</t>
+          <t>Country Regulatory Specialist, Clinical Research - 100% Remote in Brazil, English advanced</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Novartis</t>
+          <t>Syneos Health</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>New Cairo, Egypt</t>
+          <t>Remote, Brazil</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>https://novartis.wd3.myworkdayjobs.com/Novartis_Careers/job/New-Cairo/Patient-Safety-Specialist_REQ-10089513-1</t>
+          <t>https://www.syneoshealth.com/clinical-corporate-careers/jobs/18363943-country-regulatory-specialist-clinical-research-100-percent-remote-in-brazil-english-advanced</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>Good content match (pharmacy degree, no experience stated) but hybrid in Cairo, Arabic required and relocation not supported.</t>
+          <t>Needs 3-4 years of clinical research experience and a Brazil base.</t>
         </is>
       </c>
     </row>
@@ -8354,32 +7290,32 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Safety &amp; PV Specialist II - Literature Case Processing</t>
+          <t>Assistant CRA - FSP (Brazil, remote)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Syneos Health</t>
+          <t>Thermo Fisher Scientific (PPD clinical research business)</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Gurgaon, India</t>
+          <t>Brazil - Sao Paulo - Remote</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>https://www.syneoshealth.com/clinical-corporate-careers/jobs/18356662-safety-and-pv-specialist-ii-literature-case-processing</t>
+          <t>https://thermofisher.wd5.myworkdayjobs.com/ThermoFisherCareers/job/Remote-Brazil/Assistant-CRA---FSP_R-01371844</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Asks for 4-7 years of PV experience; Gurgaon location and work mode unstated.</t>
+          <t>Headline says 0-2 years but the posting makes prior oncology clinical-study experience mandatory and is Brazil-based.</t>
         </is>
       </c>
     </row>
@@ -8391,12 +7327,12 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>FSP Clinical Research Associate I / II (Israel, remote)</t>
+          <t>Medical Information Specialist with Latvian, English and Additional Language</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific (PPD clinical research business)</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -8406,17 +7342,17 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Israel - Tel Aviv - Remote</t>
+          <t>Riga, Latvia (also Lisbon, Zagreb, Athens, Barcelona, Prague, Sofia, Madrid, Bucharest)</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>https://thermofisher.wd5.myworkdayjobs.com/ThermoFisherCareers/job/Remote-Israel/FSP-Clinical-Research-Associate-I--Clinical-Research-Associate-II_R-01371946</t>
+          <t>https://iqvia.wd1.myworkdayjobs.com/IQVIA/job/Riga-Latvia/Medical-Information-Specialist-with-Latvian--English-and-Additional-Language_R1573442</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>Needs 1-2 years of actual monitoring experience and heavy site travel, plus Israel base.</t>
+          <t>Perfect on duties and degree (no experience asked), but Latvian at C2 level is a hard requirement KT almost certainly lacks. IQVIA posts the same job for other languages (Bulgarian dated 2026-10-09, German/Estonian variants), all language-gated.</t>
         </is>
       </c>
     </row>
@@ -8428,12 +7364,12 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Associate Business Consultant - Life Sciences Consulting (London)</t>
+          <t>Clinical Pharmacist (Independent Prescriber)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Veeva Systems</t>
+          <t>Montu UK (Alternaleaf)</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -8443,17 +7379,17 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>United Kingdom - London (hybrid)</t>
+          <t>Hybrid London, UK</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/veeva/ae310551-4c21-4c6e-aec5-05da7e29c0e0</t>
+          <t>https://jobs.ashbyhq.com/montu-uk/4435f8d7-0eeb-46f8-85fc-f6784ed0ba62</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Intake is limited to 2027 graduates; KT graduated in 2024 so is outside the stated target group.</t>
+          <t>Requires GPhC registration and IP qualification.</t>
         </is>
       </c>
     </row>
@@ -8465,12 +7401,12 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Implementation Operations Manager</t>
+          <t>Quality Assurance Officer (Leafio pharmaceutical wholesale)</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Vida Health</t>
+          <t>Montu UK (Leafio)</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -8480,17 +7416,17 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>United States (remote)</t>
+          <t>Winnersh, Berkshire, UK (hybrid)</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/vida/d4412486-5f81-4acd-bebf-8adbf4ae66da</t>
+          <t>https://jobs.ashbyhq.com/montu-uk/d3f2d04d-1b78-45cf-8886-1525a0d92c62</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Hard US-residence and work-authorisation rule plus 3+ years of data/implementation experience.</t>
+          <t>Pharmaceutical wholesale quality role where an MPharm background is relevant; it asks for more than 2 years in a GMDP environment, which is the main gap, so this is a stretch rather than a fit. Quality/regulatory roles are covered more fully by other role families. Audit: three separate 'proven experience' requirements (more than 2 years in a GMDP environment). Compensation also includes equity.</t>
         </is>
       </c>
     </row>
@@ -8502,32 +7438,32 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Global Value Dossiers Consultant - Global Health Economics team - UK</t>
+          <t>Patient Safety Specialist</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>IQVIA</t>
+          <t>Novartis</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>London, United Kingdom</t>
+          <t>New Cairo, Egypt</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>https://iqvia.wd1.myworkdayjobs.com/IQVIA/job/London-United-Kingdom/Global-Value-Dossiers-Consultant---Global-Health-Economics-team---UK_R1573929</t>
+          <t>https://novartis.wd3.myworkdayjobs.com/Novartis_Careers/job/New-Cairo/Patient-Safety-Specialist_REQ-10089513-1</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>Needs about 5 years of HEOR/HTA writing and no visa support is offered. Kept as a marker of what a mid-career HEOR writer role looks like.</t>
+          <t>Good content match (pharmacy degree, no experience stated) but hybrid in Cairo, Arabic required and relocation not supported.</t>
         </is>
       </c>
     </row>
@@ -8539,32 +7475,32 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Operations Manager, Product Implementation</t>
+          <t>Safety &amp; PV Specialist II - Literature Case Processing</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Lyra Health</t>
+          <t>Syneos Health</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>United States (Lever workplaceType: remote)</t>
+          <t>Gurgaon, India</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/lyrahealth/4287bc02-b22a-4da8-bbe7-cdd8a0df7f5e</t>
+          <t>https://www.syneoshealth.com/clinical-corporate-careers/jobs/18356662-safety-and-pv-specialist-ii-literature-case-processing</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>Manager level with 8+ years required.</t>
+          <t>Asks for 4-7 years of PV experience; Gurgaon location and work mode unstated.</t>
         </is>
       </c>
     </row>
@@ -8576,32 +7512,32 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Senior Regulatory Affairs Associate - Labeling Strategy</t>
+          <t>FSP Clinical Research Associate I / II (Israel, remote)</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Parexel</t>
+          <t>Thermo Fisher Scientific (PPD clinical research business)</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Bengaluru, India (Remote)</t>
+          <t>Israel - Tel Aviv - Remote</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>https://wd1.myworkdaysite.com/recruiting/parexel/Parexel_External_Careers/job/India-Bengaluru-Remote/Senior-Regulatory-Affairs-Associate_R0000043177</t>
+          <t>https://thermofisher.wd5.myworkdayjobs.com/ThermoFisherCareers/job/Remote-Israel/FSP-Clinical-Research-Associate-I--Clinical-Research-Associate-II_R-01371946</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>Asks for 7-8 years of experience; not realistic for a 2024 graduate. Listed to show what labelling roles at CROs look like.</t>
+          <t>Needs 1-2 years of actual monitoring experience and heavy site travel, plus Israel base.</t>
         </is>
       </c>
     </row>
@@ -8613,32 +7549,32 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>CMC Regulatory Affairs Associate (M3 authoring, biological products)</t>
+          <t>Associate Business Consultant - Life Sciences Consulting (London)</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Parexel</t>
+          <t>Veeva Systems</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Mexico (Remote); also Argentina-Remote and Brazil-Remote</t>
+          <t>United Kingdom - London (hybrid)</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>https://wd1.myworkdaysite.com/recruiting/parexel/Parexel_External_Careers/job/Mexico-Remote/CMC-Regulatory-Affairs-Associate--M3-Authoring-experience-for-Biological-products--_R0000046915</t>
+          <t>https://jobs.lever.co/veeva/ae310551-4c21-4c6e-aec5-05da7e29c0e0</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>Mandatory biologics CMC and M3 authoring experience plus a multi-year industry minimum; not realistic for a recent graduate.</t>
+          <t>Intake is limited to 2027 graduates; KT graduated in 2024 so is outside the stated target group.</t>
         </is>
       </c>
     </row>
@@ -8650,32 +7586,32 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Global Market Access and Pricing Associate - Dermatology - VIE Contract</t>
+          <t>Implementation Operations Manager</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Sanofi</t>
+          <t>Vida Health</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Cambridge, MA, United States (target start 01/02/2027)</t>
+          <t>United States (remote)</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>https://sanofi.wd3.myworkdayjobs.com/SanofiCareers/job/Cambridge-MA/Global-Market-Access-and-Pricing-Associate---Dermatology---VIE-Contract_R2872111</t>
+          <t>https://jobs.lever.co/vida/d4412486-5f81-4acd-bebf-8adbf4ae66da</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>Closed to anyone who is not an EEA citizen aged 18-28 (a Turkish or UK citizen is not eligible), so it is only useful if KT holds EEA citizenship; the content (market access associate, pharmacy Master's accepted) is otherwise a good model role.</t>
+          <t>Hard US-residence and work-authorisation rule plus 3+ years of data/implementation experience.</t>
         </is>
       </c>
     </row>
@@ -8687,32 +7623,32 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Medical Contact Center Assistant I</t>
+          <t>Sr Assoc Pharmacovigilance Operations</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Fortrea</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Manila (Philippines)</t>
+          <t>India - Hyderabad</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>https://fortrea.wd1.myworkdayjobs.com/Fortrea/job/Manila/Medical-Contact-Center-Assistant-I_265619</t>
+          <t>https://careers.amgen.com/en/job/hyderabad/sr-assoc-pharmacovigilance-operations/87/99202629072</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>Needs a healthcare licence (pharmacist etc.) and a year of voice call-centre experience; KT is unlicensed and the post is in Manila. The sister 'Medical call center Associate I' (265822, 2 years) has the same licence rule.</t>
+          <t>Degree-level requirement plus 2 years of related experience; one clear gap. On-site in Hyderabad, so only workable if based in or relocating to India. Same standard as the audit: 'Sr Assoc' role that requires 2 years of directly related experience, on-site only.</t>
         </is>
       </c>
     </row>
@@ -8724,7 +7660,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Study Start Up Specialist - UK IQVIA Biotech</t>
+          <t>Global Value Dossiers Consultant - Global Health Economics team - UK</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -8734,22 +7670,22 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>London / Reading, United Kingdom (home-based)</t>
+          <t>London, United Kingdom</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.iqvia.com/en/jobs/R1571744-0</t>
+          <t>https://iqvia.wd1.myworkdayjobs.com/IQVIA/job/London-United-Kingdom/Global-Value-Dossiers-Consultant---Global-Health-Economics-team---UK_R1573929</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>Needs 3 years of clinical research experience and UK submissions knowledge.</t>
+          <t>Needs about 5 years of HEOR/HTA writing and no visa support is offered. Kept as a marker of what a mid-career HEOR writer role looks like.</t>
         </is>
       </c>
     </row>
@@ -8761,32 +7697,32 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Professional Education Manager</t>
+          <t>Operations Manager, Product Implementation</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson (MedTech Surgery)</t>
+          <t>Lyra Health</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Istanbul, Turkey</t>
+          <t>United States (Lever workplaceType: remote)</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>https://www.careers.jnj.com/en/jobs/r-103824/professional-education-manager/</t>
+          <t>https://jobs.lever.co/lyrahealth/4287bc02-b22a-4da8-bbe7-cdd8a0df7f5e</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>Interesting because it is a medical-education job in Istanbul with native Turkish, but it asks for 3-5+ years and a commercial/medical-device focus, which is too senior for a 2024 graduate.</t>
+          <t>Manager level with 8+ years required.</t>
         </is>
       </c>
     </row>
@@ -8798,32 +7734,32 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Associate Regulatory Affairs Specialist (Benelux)</t>
+          <t>Senior Regulatory Affairs Associate - Labeling Strategy</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Medtronic</t>
+          <t>Parexel</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Eindhoven and Heerlen, Netherlands (text says based in Maastricht or Heerlen)</t>
+          <t>Bengaluru, India (Remote)</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>https://medtronic.wd1.myworkdayjobs.com/MedtronicCareers/job/Eindhoven-Noord-Brabant-Netherlands/Associate-Regulatory-Affairs-Specialist_R76733</t>
+          <t>https://wd1.myworkdaysite.com/recruiting/parexel/Parexel_External_Careers/job/India-Bengaluru-Remote/Senior-Regulatory-Affairs-Associate_R0000043177</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>True entry level (0+ years) but hybrid on site in the Netherlands twice a week and requires fluent Dutch; kept as a C so KT can see the entry-level device RA pattern.</t>
+          <t>Asks for 7-8 years of experience; not realistic for a 2024 graduate. Listed to show what labelling roles at CROs look like.</t>
         </is>
       </c>
     </row>
@@ -8835,32 +7771,32 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Sr. Provider Operations Specialist (Remote)</t>
+          <t>CMC Regulatory Affairs Associate (M3 authoring, biological products)</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Rula</t>
+          <t>Parexel</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Remote - United States (not Hawaii)</t>
+          <t>Mexico (Remote); also Argentina-Remote and Brazil-Remote</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/rula/cf5ce949-20f4-4e27-bd1a-6bd62a15ee93</t>
+          <t>https://wd1.myworkdaysite.com/recruiting/parexel/Parexel_External_Careers/job/Mexico-Remote/CMC-Regulatory-Affairs-Associate--M3-Authoring-experience-for-Biological-products--_R0000046915</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>US-only and 3+ years required.</t>
+          <t>Mandatory biologics CMC and M3 authoring experience plus a multi-year industry minimum; not realistic for a recent graduate.</t>
         </is>
       </c>
     </row>
@@ -8872,30 +7808,289 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
+          <t>Local Contact Person for Pharmacovigilance and Regulatory Affairs (Contractor; Berlin, Paris, Brussels, Ljubljana, Athens, Budapest)</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>PrimeVigilance (Ergomed Group)</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Remote flag in Berlin DE, Paris FR, Brussels BE, Ljubljana SI, Athens GR, Budapest HU (one posting per country)</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Ergomed/744000155310319-local-contact-person-for-pharmacovigilance-and-regulatory-affairs-contractor-</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>Needs 3+ years of PV experience and local-country residency; contractor role.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Global Market Access and Pricing Associate - Dermatology - VIE Contract</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Sanofi</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Cambridge, MA, United States (target start 01/02/2027)</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>https://sanofi.wd3.myworkdayjobs.com/SanofiCareers/job/Cambridge-MA/Global-Market-Access-and-Pricing-Associate---Dermatology---VIE-Contract_R2872111</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>Closed to anyone who is not an EEA citizen aged 18-28 (a Turkish or UK citizen is not eligible), so it is only useful if KT holds EEA citizenship; the content (market access associate, pharmacy Master's accepted) is otherwise a good model role.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Medical Contact Center Assistant I</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Fortrea</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Manila (Philippines)</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>https://fortrea.wd1.myworkdayjobs.com/Fortrea/job/Manila/Medical-Contact-Center-Assistant-I_265619</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>Needs a healthcare licence (pharmacist etc.) and a year of voice call-centre experience; KT is unlicensed and the post is in Manila. The sister 'Medical call center Associate I' (265822, 2 years) has the same licence rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Study Start Up Specialist - UK IQVIA Biotech</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>IQVIA</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>London / Reading, United Kingdom (home-based)</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>https://jobs.iqvia.com/en/jobs/R1571744-0</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>Needs 3 years of clinical research experience and UK submissions knowledge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Professional Education Manager</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Johnson &amp; Johnson (MedTech Surgery)</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Istanbul, Turkey</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>https://www.careers.jnj.com/en/jobs/r-103824/professional-education-manager/</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>Interesting because it is a medical-education job in Istanbul with native Turkish, but it asks for 3-5+ years and a commercial/medical-device focus, which is too senior for a 2024 graduate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Associate Regulatory Affairs Specialist (Benelux)</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Medtronic</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Eindhoven and Heerlen, Netherlands (text says based in Maastricht or Heerlen)</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>https://medtronic.wd1.myworkdayjobs.com/MedtronicCareers/job/Eindhoven-Noord-Brabant-Netherlands/Associate-Regulatory-Affairs-Specialist_R76733</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>True entry level (0+ years) but hybrid on site in the Netherlands twice a week and requires fluent Dutch; kept as a C so KT can see the entry-level device RA pattern.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Sr. Provider Operations Specialist (Remote)</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>Rula</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Remote - United States (not Hawaii)</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/rula/cf5ce949-20f4-4e27-bd1a-6bd62a15ee93</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>US-only and 3+ years required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
           <t>Senior Regulatory Affairs Specialist</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t>Thermo Fisher Scientific (PPD clinical research)</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="D42" s="3" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="E35" s="3" t="inlineStr">
+      <c r="E42" s="3" t="inlineStr">
         <is>
           <t>Sofia, Bulgaria</t>
         </is>
       </c>
-      <c r="F35" s="3" t="inlineStr">
+      <c r="F42" s="3" t="inlineStr">
         <is>
           <t>https://thermofisher.wd5.myworkdayjobs.com/ThermoFisherCareers/job/Sofia-Bulgaria/Senior-Regulatory-Affairs-Specialist_R-01369851-1</t>
         </is>
       </c>
-      <c r="G35" s="3" t="inlineStr">
+      <c r="G42" s="3" t="inlineStr">
         <is>
           <t>Senior level asking 5+ years of experience.</t>
         </is>
